--- a/code/vocab_csv/ai.xlsx
+++ b/code/vocab_csv/ai.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="1145">
   <si>
     <t>Term</t>
   </si>
@@ -1160,6 +1160,18 @@
     <t>Capabilities that are inherently about humans or oriented towards human characteristics and activities</t>
   </si>
   <si>
+    <t>HumanIdentification</t>
+  </si>
+  <si>
+    <t>Human Identification</t>
+  </si>
+  <si>
+    <t>Capability of a system that aims to identify a human whether at an individual or group level</t>
+  </si>
+  <si>
+    <t>ai:HumanOrientedCapability</t>
+  </si>
+  <si>
     <t>BehaviourAnalysis</t>
   </si>
   <si>
@@ -1169,9 +1181,6 @@
     <t>Capability of a system in analysing people's behaviour</t>
   </si>
   <si>
-    <t>ai:HumanOrientedCapability</t>
-  </si>
-  <si>
     <t>BiometricCapability</t>
   </si>
   <si>
@@ -1200,6 +1209,9 @@
   </si>
   <si>
     <t>Capability involving automated recognition of physical, physiological and behavioural human features such as the face, eye movement, body shape, voice, prosody, gait, posture, heart rate, blood pressure, odour, keystrokes characteristics, for the purpose of establishing an individual’s identity by comparing biometric data of that individual to stored biometric data of individuals in a reference database, irrespective of whether the individual has given its consent or not</t>
+  </si>
+  <si>
+    <t>ai:BiometricCapability,ai:HumanIdentification</t>
   </si>
   <si>
     <r>
@@ -1977,6 +1989,57 @@
     <t>This concept is a stub</t>
   </si>
   <si>
+    <t xml:space="preserve">BiasAssessment </t>
+  </si>
+  <si>
+    <t>Bias Assessment</t>
+  </si>
+  <si>
+    <t>Examination of a data set, model, or AI system for bias</t>
+  </si>
+  <si>
+    <t>dpv:DataQualityAssessment</t>
+  </si>
+  <si>
+    <t>dpv:OrganisationalMeasure</t>
+  </si>
+  <si>
+    <t>BiasDetection</t>
+  </si>
+  <si>
+    <t>Bias Detection</t>
+  </si>
+  <si>
+    <t>Indicates measures to detect bias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai:BiasAssessment </t>
+  </si>
+  <si>
+    <t>BiasPrevention</t>
+  </si>
+  <si>
+    <t>Bias Prevention</t>
+  </si>
+  <si>
+    <t>Indicates measures to prevent bias</t>
+  </si>
+  <si>
+    <t>BiasMitigation</t>
+  </si>
+  <si>
+    <t>Bias Mitigation</t>
+  </si>
+  <si>
+    <t>Indicates measures to mitigate bias</t>
+  </si>
+  <si>
+    <t>Benchmarking</t>
+  </si>
+  <si>
+    <t>Measure where performance and outputs are compared to best practices, gold standards, or other forms of desired quality</t>
+  </si>
+  <si>
     <t>LifecycleStage</t>
   </si>
   <si>
@@ -2996,6 +3059,42 @@
   </si>
   <si>
     <t>ai:ModelInteractionBias</t>
+  </si>
+  <si>
+    <t>ExplainabilityRisk</t>
+  </si>
+  <si>
+    <t>Explainability Risk</t>
+  </si>
+  <si>
+    <t>Risk that an AI system’s decisions or behaviors cannot be adequately understood, interpreted, or justified by relevant stakeholders.</t>
+  </si>
+  <si>
+    <t>ModelPoisoning</t>
+  </si>
+  <si>
+    <t>Model Poisoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attacks trying to manipulate pre-trained components used in training </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai:SecurityAttack </t>
+  </si>
+  <si>
+    <t>AI Act, Article 15(5)</t>
+  </si>
+  <si>
+    <t>ConfidentialityAttack</t>
+  </si>
+  <si>
+    <t>Confidentiality Attack</t>
+  </si>
+  <si>
+    <t>ModelFlaw</t>
+  </si>
+  <si>
+    <t>Model Flaw</t>
   </si>
   <si>
     <t>IRI</t>
@@ -3550,7 +3649,7 @@
       <color rgb="FF0000FF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3573,6 +3672,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -3632,7 +3737,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3757,7 +3862,13 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -4635,16 +4746,16 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>205</v>
@@ -4664,7 +4775,7 @@
         <v>32</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="O2" s="26"/>
       <c r="P2" s="26"/>
@@ -4687,16 +4798,16 @@
     </row>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>205</v>
@@ -4770,13 +4881,13 @@
     </row>
     <row r="5">
       <c r="A5" s="27" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="26" t="s">
@@ -4818,16 +4929,16 @@
     </row>
     <row r="6">
       <c r="A6" s="27" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>205</v>
@@ -4868,16 +4979,16 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>205</v>
@@ -4918,16 +5029,16 @@
     </row>
     <row r="8">
       <c r="A8" s="27" t="s">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>205</v>
@@ -4968,16 +5079,16 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>205</v>
@@ -5018,16 +5129,16 @@
     </row>
     <row r="10">
       <c r="A10" s="27" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>205</v>
@@ -5068,16 +5179,16 @@
     </row>
     <row r="11">
       <c r="A11" s="27" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>205</v>
@@ -5118,16 +5229,16 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="s">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>205</v>
@@ -5168,16 +5279,16 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>205</v>
@@ -5217,7 +5328,7 @@
       <c r="AF13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="43"/>
+      <c r="A14" s="45"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:AF135">
@@ -5277,10 +5388,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
@@ -5312,51 +5423,51 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="44"/>
+      <c r="F2" s="46"/>
       <c r="G2" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="H2" s="44"/>
+        <v>744</v>
+      </c>
+      <c r="H2" s="46"/>
       <c r="I2" s="8"/>
-      <c r="J2" s="44"/>
+      <c r="J2" s="46"/>
       <c r="M2" s="41">
         <v>45410.0</v>
       </c>
-      <c r="N2" s="44"/>
+      <c r="N2" s="46"/>
       <c r="O2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46"/>
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="7"/>
@@ -5367,23 +5478,23 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
@@ -5456,23 +5567,23 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="26"/>
@@ -5510,23 +5621,23 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
@@ -5564,23 +5675,23 @@
     </row>
     <row r="8">
       <c r="A8" s="27" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
@@ -5618,23 +5729,23 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
@@ -5672,23 +5783,23 @@
     </row>
     <row r="10">
       <c r="A10" s="27" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="B10" s="27" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>743</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>744</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>722</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
@@ -5726,22 +5837,22 @@
     </row>
     <row r="11">
       <c r="A11" s="27" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
@@ -5781,23 +5892,23 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
@@ -5835,23 +5946,23 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
@@ -5889,23 +6000,23 @@
     </row>
     <row r="14">
       <c r="A14" s="27" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>756</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>735</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -5943,23 +6054,23 @@
     </row>
     <row r="15">
       <c r="A15" s="27" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
@@ -5997,23 +6108,23 @@
     </row>
     <row r="16">
       <c r="A16" s="27" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
@@ -6051,22 +6162,22 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>764</v>
+        <v>785</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="M17" s="9">
         <v>45627.0</v>
@@ -6083,23 +6194,23 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>768</v>
+        <v>789</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -6137,23 +6248,23 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -6191,23 +6302,23 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -6248,23 +6359,23 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -6302,23 +6413,23 @@
     </row>
     <row r="23">
       <c r="A23" s="27" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -6356,23 +6467,23 @@
     </row>
     <row r="24">
       <c r="A24" s="27" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -6410,23 +6521,23 @@
     </row>
     <row r="25">
       <c r="A25" s="27" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -6464,23 +6575,23 @@
     </row>
     <row r="26">
       <c r="A26" s="27" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -6518,22 +6629,22 @@
     </row>
     <row r="27">
       <c r="A27" s="27" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="M27" s="9">
         <v>45627.0</v>
@@ -6550,23 +6661,23 @@
     </row>
     <row r="28">
       <c r="A28" s="27" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -6604,23 +6715,23 @@
     </row>
     <row r="29">
       <c r="A29" s="27" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -6658,23 +6769,23 @@
     </row>
     <row r="30">
       <c r="A30" s="27" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>781</v>
-      </c>
       <c r="E30" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -6712,23 +6823,23 @@
     </row>
     <row r="31">
       <c r="A31" s="27" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -6766,23 +6877,23 @@
     </row>
     <row r="32">
       <c r="A32" s="27" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -6820,22 +6931,22 @@
     </row>
     <row r="33">
       <c r="A33" s="27" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="M33" s="9">
         <v>45627.0</v>
@@ -6852,23 +6963,23 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>814</v>
+        <v>835</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -6906,23 +7017,23 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>815</v>
+        <v>836</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -6960,23 +7071,23 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
@@ -7018,23 +7129,23 @@
     </row>
     <row r="38">
       <c r="A38" s="37" t="s">
-        <v>821</v>
+        <v>842</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>823</v>
+        <v>844</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
@@ -7072,23 +7183,23 @@
     </row>
     <row r="39">
       <c r="A39" s="27" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -7126,23 +7237,23 @@
     </row>
     <row r="40">
       <c r="A40" s="27" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -7180,23 +7291,23 @@
     </row>
     <row r="41">
       <c r="A41" s="27" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -7234,23 +7345,23 @@
     </row>
     <row r="42">
       <c r="A42" s="27" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>835</v>
+        <v>856</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>836</v>
+        <v>857</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -7288,22 +7399,22 @@
     </row>
     <row r="43">
       <c r="A43" s="27" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>839</v>
+        <v>860</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="M43" s="9">
         <v>45627.0</v>
@@ -7320,23 +7431,23 @@
     </row>
     <row r="44">
       <c r="A44" s="27" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -7374,23 +7485,23 @@
     </row>
     <row r="45">
       <c r="A45" s="27" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -7428,23 +7539,23 @@
     </row>
     <row r="46">
       <c r="A46" s="27" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>827</v>
-      </c>
       <c r="E46" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
@@ -7482,23 +7593,23 @@
     </row>
     <row r="47">
       <c r="A47" s="27" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -7536,23 +7647,23 @@
     </row>
     <row r="48">
       <c r="A48" s="27" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
@@ -7590,22 +7701,22 @@
     </row>
     <row r="49">
       <c r="A49" s="27" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="M49" s="9">
         <v>45627.0</v>
@@ -7622,23 +7733,23 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>858</v>
+        <v>879</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
@@ -7676,23 +7787,23 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
@@ -7730,23 +7841,23 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
@@ -7787,23 +7898,23 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -7841,26 +7952,26 @@
     </row>
     <row r="55">
       <c r="A55" s="27" t="s">
-        <v>870</v>
+        <v>891</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>871</v>
+        <v>892</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>872</v>
+        <v>893</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F55" s="26"/>
       <c r="G55" s="27" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="I55" s="26"/>
       <c r="J55" s="26"/>
@@ -7897,26 +8008,26 @@
     </row>
     <row r="56">
       <c r="A56" s="27" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F56" s="26"/>
       <c r="G56" s="27" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="H56" s="27" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="I56" s="26"/>
       <c r="J56" s="26"/>
@@ -7953,31 +8064,31 @@
     </row>
     <row r="57">
       <c r="A57" s="27" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F57" s="26"/>
       <c r="G57" s="27" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
       <c r="K57" s="6" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="L57" s="26"/>
       <c r="M57" s="9">
@@ -8011,31 +8122,31 @@
     </row>
     <row r="58">
       <c r="A58" s="27" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F58" s="26"/>
       <c r="G58" s="27" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I58" s="26"/>
       <c r="J58" s="26"/>
       <c r="K58" s="30" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="L58" s="26"/>
       <c r="M58" s="9">
@@ -8072,23 +8183,23 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
@@ -8129,23 +8240,23 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
@@ -8186,23 +8297,23 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
@@ -8240,23 +8351,23 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>898</v>
-      </c>
-      <c r="C66" s="45" t="s">
-        <v>899</v>
+        <v>919</v>
+      </c>
+      <c r="C66" s="47" t="s">
+        <v>920</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F66" s="11"/>
       <c r="G66" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H66" s="11"/>
       <c r="K66" s="11"/>
@@ -8269,7 +8380,7 @@
         <v>21</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
@@ -8291,31 +8402,31 @@
       <c r="AH66" s="7"/>
     </row>
     <row r="67">
-      <c r="A67" s="45" t="s">
-        <v>902</v>
-      </c>
-      <c r="B67" s="45" t="s">
-        <v>903</v>
-      </c>
-      <c r="C67" s="46" t="s">
-        <v>904</v>
-      </c>
-      <c r="D67" s="46" t="s">
-        <v>905</v>
+      <c r="A67" s="47" t="s">
+        <v>923</v>
+      </c>
+      <c r="B67" s="47" t="s">
+        <v>924</v>
+      </c>
+      <c r="C67" s="48" t="s">
+        <v>925</v>
+      </c>
+      <c r="D67" s="48" t="s">
+        <v>926</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F67" s="11"/>
       <c r="G67" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H67" s="11"/>
       <c r="K67" s="11"/>
-      <c r="L67" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M67" s="47">
+      <c r="L67" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M67" s="49">
         <v>45548.0</v>
       </c>
       <c r="N67" s="39">
@@ -8325,7 +8436,7 @@
         <v>32</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
@@ -8345,31 +8456,31 @@
       <c r="AF67" s="26"/>
     </row>
     <row r="68">
-      <c r="A68" s="45" t="s">
-        <v>907</v>
-      </c>
-      <c r="B68" s="45" t="s">
-        <v>908</v>
-      </c>
-      <c r="C68" s="45" t="s">
-        <v>909</v>
-      </c>
-      <c r="D68" s="46" t="s">
-        <v>910</v>
+      <c r="A68" s="47" t="s">
+        <v>928</v>
+      </c>
+      <c r="B68" s="47" t="s">
+        <v>929</v>
+      </c>
+      <c r="C68" s="47" t="s">
+        <v>930</v>
+      </c>
+      <c r="D68" s="48" t="s">
+        <v>931</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F68" s="11"/>
       <c r="G68" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H68" s="11"/>
       <c r="K68" s="11"/>
-      <c r="L68" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M68" s="47">
+      <c r="L68" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M68" s="49">
         <v>45548.0</v>
       </c>
       <c r="N68" s="17"/>
@@ -8377,7 +8488,7 @@
         <v>21</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
@@ -8399,31 +8510,31 @@
       <c r="AH68" s="7"/>
     </row>
     <row r="69">
-      <c r="A69" s="46" t="s">
-        <v>911</v>
-      </c>
-      <c r="B69" s="46" t="s">
-        <v>912</v>
-      </c>
-      <c r="C69" s="45" t="s">
-        <v>913</v>
-      </c>
-      <c r="D69" s="46" t="s">
-        <v>914</v>
+      <c r="A69" s="48" t="s">
+        <v>932</v>
+      </c>
+      <c r="B69" s="48" t="s">
+        <v>933</v>
+      </c>
+      <c r="C69" s="47" t="s">
+        <v>934</v>
+      </c>
+      <c r="D69" s="48" t="s">
+        <v>935</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F69" s="11"/>
       <c r="G69" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H69" s="11"/>
       <c r="K69" s="11"/>
-      <c r="L69" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M69" s="47">
+      <c r="L69" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M69" s="49">
         <v>45548.0</v>
       </c>
       <c r="N69" s="39">
@@ -8433,7 +8544,7 @@
         <v>32</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q69" s="11"/>
       <c r="R69" s="11"/>
@@ -8453,31 +8564,31 @@
       <c r="AF69" s="26"/>
     </row>
     <row r="70">
-      <c r="A70" s="45" t="s">
-        <v>915</v>
-      </c>
-      <c r="B70" s="45" t="s">
-        <v>916</v>
-      </c>
-      <c r="C70" s="45" t="s">
-        <v>917</v>
-      </c>
-      <c r="D70" s="46" t="s">
-        <v>914</v>
+      <c r="A70" s="47" t="s">
+        <v>936</v>
+      </c>
+      <c r="B70" s="47" t="s">
+        <v>937</v>
+      </c>
+      <c r="C70" s="47" t="s">
+        <v>938</v>
+      </c>
+      <c r="D70" s="48" t="s">
+        <v>935</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F70" s="11"/>
       <c r="G70" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H70" s="11"/>
       <c r="K70" s="11"/>
-      <c r="L70" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M70" s="47">
+      <c r="L70" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M70" s="49">
         <v>45548.0</v>
       </c>
       <c r="N70" s="17"/>
@@ -8485,7 +8596,7 @@
         <v>21</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q70" s="11"/>
       <c r="R70" s="11"/>
@@ -8507,33 +8618,33 @@
       <c r="AH70" s="7"/>
     </row>
     <row r="71">
-      <c r="A71" s="46" t="s">
-        <v>918</v>
-      </c>
-      <c r="B71" s="46" t="s">
-        <v>919</v>
-      </c>
-      <c r="C71" s="45" t="s">
-        <v>920</v>
-      </c>
-      <c r="D71" s="46" t="s">
-        <v>914</v>
+      <c r="A71" s="48" t="s">
+        <v>939</v>
+      </c>
+      <c r="B71" s="48" t="s">
+        <v>940</v>
+      </c>
+      <c r="C71" s="47" t="s">
+        <v>941</v>
+      </c>
+      <c r="D71" s="48" t="s">
+        <v>935</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F71" s="11"/>
       <c r="G71" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H71" s="11"/>
-      <c r="K71" s="45" t="s">
-        <v>921</v>
-      </c>
-      <c r="L71" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M71" s="47">
+      <c r="K71" s="47" t="s">
+        <v>942</v>
+      </c>
+      <c r="L71" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M71" s="49">
         <v>45548.0</v>
       </c>
       <c r="N71" s="39">
@@ -8543,7 +8654,7 @@
         <v>32</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q71" s="11"/>
       <c r="R71" s="11"/>
@@ -8563,31 +8674,31 @@
       <c r="AF71" s="26"/>
     </row>
     <row r="72">
-      <c r="A72" s="45" t="s">
-        <v>922</v>
-      </c>
-      <c r="B72" s="45" t="s">
-        <v>923</v>
-      </c>
-      <c r="C72" s="45" t="s">
-        <v>924</v>
-      </c>
-      <c r="D72" s="46" t="s">
-        <v>914</v>
+      <c r="A72" s="47" t="s">
+        <v>943</v>
+      </c>
+      <c r="B72" s="47" t="s">
+        <v>944</v>
+      </c>
+      <c r="C72" s="47" t="s">
+        <v>945</v>
+      </c>
+      <c r="D72" s="48" t="s">
+        <v>935</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F72" s="11"/>
       <c r="G72" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H72" s="11"/>
       <c r="K72" s="11"/>
-      <c r="L72" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M72" s="47">
+      <c r="L72" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M72" s="49">
         <v>45548.0</v>
       </c>
       <c r="N72" s="17"/>
@@ -8595,7 +8706,7 @@
         <v>21</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q72" s="11"/>
       <c r="R72" s="11"/>
@@ -8617,31 +8728,31 @@
       <c r="AH72" s="7"/>
     </row>
     <row r="73">
-      <c r="A73" s="45" t="s">
-        <v>925</v>
-      </c>
-      <c r="B73" s="45" t="s">
-        <v>926</v>
-      </c>
-      <c r="C73" s="45" t="s">
-        <v>927</v>
-      </c>
-      <c r="D73" s="46" t="s">
-        <v>914</v>
+      <c r="A73" s="47" t="s">
+        <v>946</v>
+      </c>
+      <c r="B73" s="47" t="s">
+        <v>947</v>
+      </c>
+      <c r="C73" s="47" t="s">
+        <v>948</v>
+      </c>
+      <c r="D73" s="48" t="s">
+        <v>935</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F73" s="11"/>
       <c r="G73" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H73" s="11"/>
       <c r="K73" s="11"/>
-      <c r="L73" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M73" s="47">
+      <c r="L73" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M73" s="49">
         <v>45548.0</v>
       </c>
       <c r="N73" s="17"/>
@@ -8649,7 +8760,7 @@
         <v>21</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q73" s="11"/>
       <c r="R73" s="11"/>
@@ -8671,33 +8782,33 @@
       <c r="AH73" s="7"/>
     </row>
     <row r="74">
-      <c r="A74" s="45" t="s">
-        <v>928</v>
-      </c>
-      <c r="B74" s="45" t="s">
-        <v>929</v>
-      </c>
-      <c r="C74" s="45" t="s">
-        <v>930</v>
-      </c>
-      <c r="D74" s="46" t="s">
-        <v>910</v>
+      <c r="A74" s="47" t="s">
+        <v>949</v>
+      </c>
+      <c r="B74" s="47" t="s">
+        <v>950</v>
+      </c>
+      <c r="C74" s="47" t="s">
+        <v>951</v>
+      </c>
+      <c r="D74" s="48" t="s">
+        <v>931</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F74" s="11"/>
       <c r="G74" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H74" s="11"/>
-      <c r="K74" s="45" t="s">
-        <v>931</v>
-      </c>
-      <c r="L74" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M74" s="47">
+      <c r="K74" s="47" t="s">
+        <v>952</v>
+      </c>
+      <c r="L74" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M74" s="49">
         <v>45548.0</v>
       </c>
       <c r="N74" s="17"/>
@@ -8705,7 +8816,7 @@
         <v>21</v>
       </c>
       <c r="P74" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q74" s="11"/>
       <c r="R74" s="11"/>
@@ -8727,31 +8838,31 @@
       <c r="AH74" s="7"/>
     </row>
     <row r="75">
-      <c r="A75" s="45" t="s">
-        <v>932</v>
-      </c>
-      <c r="B75" s="45" t="s">
-        <v>933</v>
-      </c>
-      <c r="C75" s="45" t="s">
-        <v>934</v>
-      </c>
-      <c r="D75" s="46" t="s">
-        <v>935</v>
+      <c r="A75" s="47" t="s">
+        <v>953</v>
+      </c>
+      <c r="B75" s="47" t="s">
+        <v>954</v>
+      </c>
+      <c r="C75" s="47" t="s">
+        <v>955</v>
+      </c>
+      <c r="D75" s="48" t="s">
+        <v>956</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F75" s="11"/>
       <c r="G75" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H75" s="11"/>
       <c r="K75" s="11"/>
-      <c r="L75" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M75" s="47">
+      <c r="L75" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M75" s="49">
         <v>45548.0</v>
       </c>
       <c r="N75" s="17"/>
@@ -8759,7 +8870,7 @@
         <v>21</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q75" s="11"/>
       <c r="R75" s="11"/>
@@ -8781,31 +8892,31 @@
       <c r="AH75" s="7"/>
     </row>
     <row r="76">
-      <c r="A76" s="45" t="s">
-        <v>936</v>
-      </c>
-      <c r="B76" s="45" t="s">
-        <v>937</v>
-      </c>
-      <c r="C76" s="45" t="s">
-        <v>938</v>
-      </c>
-      <c r="D76" s="46" t="s">
-        <v>935</v>
+      <c r="A76" s="47" t="s">
+        <v>957</v>
+      </c>
+      <c r="B76" s="47" t="s">
+        <v>958</v>
+      </c>
+      <c r="C76" s="47" t="s">
+        <v>959</v>
+      </c>
+      <c r="D76" s="48" t="s">
+        <v>956</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F76" s="11"/>
       <c r="G76" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H76" s="11"/>
       <c r="K76" s="11"/>
-      <c r="L76" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M76" s="47">
+      <c r="L76" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M76" s="49">
         <v>45548.0</v>
       </c>
       <c r="N76" s="17"/>
@@ -8813,7 +8924,7 @@
         <v>21</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q76" s="11"/>
       <c r="R76" s="11"/>
@@ -8835,31 +8946,31 @@
       <c r="AH76" s="7"/>
     </row>
     <row r="77">
-      <c r="A77" s="45" t="s">
-        <v>939</v>
-      </c>
-      <c r="B77" s="45" t="s">
-        <v>940</v>
-      </c>
-      <c r="C77" s="45" t="s">
-        <v>941</v>
-      </c>
-      <c r="D77" s="46" t="s">
-        <v>935</v>
+      <c r="A77" s="47" t="s">
+        <v>960</v>
+      </c>
+      <c r="B77" s="47" t="s">
+        <v>961</v>
+      </c>
+      <c r="C77" s="47" t="s">
+        <v>962</v>
+      </c>
+      <c r="D77" s="48" t="s">
+        <v>956</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F77" s="11"/>
       <c r="G77" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H77" s="11"/>
       <c r="K77" s="11"/>
-      <c r="L77" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M77" s="47">
+      <c r="L77" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M77" s="49">
         <v>45548.0</v>
       </c>
       <c r="N77" s="17"/>
@@ -8867,7 +8978,7 @@
         <v>21</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q77" s="11"/>
       <c r="R77" s="11"/>
@@ -8889,33 +9000,33 @@
       <c r="AH77" s="7"/>
     </row>
     <row r="78">
-      <c r="A78" s="45" t="s">
-        <v>942</v>
-      </c>
-      <c r="B78" s="45" t="s">
-        <v>943</v>
-      </c>
-      <c r="C78" s="45" t="s">
-        <v>944</v>
-      </c>
-      <c r="D78" s="46" t="s">
-        <v>935</v>
+      <c r="A78" s="47" t="s">
+        <v>963</v>
+      </c>
+      <c r="B78" s="47" t="s">
+        <v>964</v>
+      </c>
+      <c r="C78" s="47" t="s">
+        <v>965</v>
+      </c>
+      <c r="D78" s="48" t="s">
+        <v>956</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F78" s="11"/>
       <c r="G78" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H78" s="11"/>
-      <c r="K78" s="45" t="s">
-        <v>945</v>
-      </c>
-      <c r="L78" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M78" s="47">
+      <c r="K78" s="47" t="s">
+        <v>966</v>
+      </c>
+      <c r="L78" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M78" s="49">
         <v>45548.0</v>
       </c>
       <c r="N78" s="17"/>
@@ -8923,7 +9034,7 @@
         <v>21</v>
       </c>
       <c r="P78" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q78" s="11"/>
       <c r="R78" s="11"/>
@@ -8945,31 +9056,31 @@
       <c r="AH78" s="7"/>
     </row>
     <row r="79">
-      <c r="A79" s="45" t="s">
-        <v>946</v>
-      </c>
-      <c r="B79" s="45" t="s">
-        <v>947</v>
-      </c>
-      <c r="C79" s="45" t="s">
-        <v>948</v>
-      </c>
-      <c r="D79" s="46" t="s">
-        <v>935</v>
+      <c r="A79" s="47" t="s">
+        <v>967</v>
+      </c>
+      <c r="B79" s="47" t="s">
+        <v>968</v>
+      </c>
+      <c r="C79" s="47" t="s">
+        <v>969</v>
+      </c>
+      <c r="D79" s="48" t="s">
+        <v>956</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F79" s="11"/>
       <c r="G79" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H79" s="11"/>
       <c r="K79" s="11"/>
-      <c r="L79" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M79" s="47">
+      <c r="L79" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M79" s="49">
         <v>45548.0</v>
       </c>
       <c r="N79" s="17"/>
@@ -8977,7 +9088,7 @@
         <v>21</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q79" s="11"/>
       <c r="R79" s="11"/>
@@ -8999,31 +9110,31 @@
       <c r="AH79" s="7"/>
     </row>
     <row r="80">
-      <c r="A80" s="45" t="s">
-        <v>949</v>
-      </c>
-      <c r="B80" s="45" t="s">
-        <v>950</v>
-      </c>
-      <c r="C80" s="45" t="s">
-        <v>951</v>
-      </c>
-      <c r="D80" s="46" t="s">
-        <v>935</v>
+      <c r="A80" s="47" t="s">
+        <v>970</v>
+      </c>
+      <c r="B80" s="47" t="s">
+        <v>971</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>972</v>
+      </c>
+      <c r="D80" s="48" t="s">
+        <v>956</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F80" s="11"/>
       <c r="G80" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H80" s="11"/>
       <c r="K80" s="11"/>
-      <c r="L80" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M80" s="47">
+      <c r="L80" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M80" s="49">
         <v>45548.0</v>
       </c>
       <c r="N80" s="17"/>
@@ -9031,7 +9142,7 @@
         <v>21</v>
       </c>
       <c r="P80" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q80" s="11"/>
       <c r="R80" s="11"/>
@@ -9053,31 +9164,31 @@
       <c r="AH80" s="7"/>
     </row>
     <row r="81">
-      <c r="A81" s="45" t="s">
-        <v>952</v>
-      </c>
-      <c r="B81" s="45" t="s">
-        <v>953</v>
-      </c>
-      <c r="C81" s="45" t="s">
-        <v>954</v>
-      </c>
-      <c r="D81" s="46" t="s">
-        <v>955</v>
+      <c r="A81" s="47" t="s">
+        <v>973</v>
+      </c>
+      <c r="B81" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="C81" s="47" t="s">
+        <v>975</v>
+      </c>
+      <c r="D81" s="48" t="s">
+        <v>976</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="F81" s="11"/>
       <c r="G81" s="10" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="H81" s="11"/>
       <c r="K81" s="11"/>
-      <c r="L81" s="45" t="s">
-        <v>906</v>
-      </c>
-      <c r="M81" s="47">
+      <c r="L81" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="M81" s="49">
         <v>45548.0</v>
       </c>
       <c r="N81" s="17"/>
@@ -9085,7 +9196,7 @@
         <v>21</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="Q81" s="11"/>
       <c r="R81" s="11"/>
@@ -9106,23 +9217,137 @@
       <c r="AG81" s="7"/>
       <c r="AH81" s="7"/>
     </row>
+    <row r="83">
+      <c r="A83" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="B83" s="42" t="s">
+        <v>978</v>
+      </c>
+      <c r="C83" s="42" t="s">
+        <v>979</v>
+      </c>
+      <c r="D83" s="7"/>
+      <c r="E83" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="F83" s="7"/>
+      <c r="G83" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="9">
+        <v>46062.0</v>
+      </c>
+      <c r="N83" s="7"/>
+      <c r="O83" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7"/>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7"/>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="7"/>
+      <c r="AA83" s="7"/>
+      <c r="AB83" s="7"/>
+      <c r="AC83" s="7"/>
+      <c r="AD83" s="7"/>
+      <c r="AE83" s="7"/>
+      <c r="AF83" s="7"/>
+      <c r="AG83" s="7"/>
+      <c r="AH83" s="7"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="s">
+        <v>980</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>981</v>
+      </c>
+      <c r="C85" s="42" t="s">
+        <v>982</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>983</v>
+      </c>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="s">
+        <v>985</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>986</v>
+      </c>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26" t="s">
+        <v>983</v>
+      </c>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="26" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="s">
+        <v>987</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>988</v>
+      </c>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="27" t="s">
+        <v>744</v>
+      </c>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="26" t="s">
+        <v>984</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A66:AF81">
+  <conditionalFormatting sqref="A66:AF81 E83">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$M66="accepted"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66:AB81">
+  <conditionalFormatting sqref="A66:AB81 E83">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$M66="proposed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66:AB81">
+  <conditionalFormatting sqref="A66:AB81 E83">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$M66="changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66:AF81">
+  <conditionalFormatting sqref="A66:AF81 E83">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>$M66="deprecated"</formula>
     </cfRule>
@@ -9192,57 +9417,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="40" t="s">
-        <v>956</v>
+        <v>989</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>957</v>
+        <v>990</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>958</v>
+        <v>991</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>959</v>
+        <v>992</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>960</v>
+        <v>993</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>961</v>
+        <v>994</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>962</v>
+        <v>995</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="48" t="s">
-        <v>963</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>964</v>
+      <c r="A2" s="50" t="s">
+        <v>996</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>997</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>965</v>
-      </c>
-      <c r="D2" s="50"/>
+        <v>998</v>
+      </c>
+      <c r="D2" s="52"/>
       <c r="E2" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="s">
-        <v>966</v>
+      <c r="A3" s="53" t="s">
+        <v>999</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>967</v>
+        <v>1000</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>968</v>
+        <v>1001</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>85</v>
@@ -9251,24 +9476,24 @@
         <v>214</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>970</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="s">
-        <v>971</v>
+      <c r="A4" s="53" t="s">
+        <v>1004</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>85</v>
@@ -9277,21 +9502,21 @@
         <v>309</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="s">
-        <v>975</v>
+      <c r="A5" s="53" t="s">
+        <v>1008</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>977</v>
+        <v>1010</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>85</v>
@@ -9300,24 +9525,24 @@
         <v>85</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>978</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="s">
-        <v>979</v>
+      <c r="A6" s="53" t="s">
+        <v>1012</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>981</v>
+        <v>1014</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>85</v>
@@ -9326,73 +9551,73 @@
         <v>85</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>982</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="s">
-        <v>983</v>
+      <c r="A7" s="53" t="s">
+        <v>1016</v>
       </c>
       <c r="B7" s="40" t="s">
         <v>311</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>984</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>985</v>
+        <v>1018</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="s">
-        <v>986</v>
+      <c r="A8" s="53" t="s">
+        <v>1019</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>988</v>
+        <v>1021</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="s">
-        <v>989</v>
+      <c r="A9" s="53" t="s">
+        <v>1022</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>990</v>
+        <v>1023</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>81</v>
@@ -9401,47 +9626,47 @@
         <v>81</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>991</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="s">
-        <v>992</v>
+      <c r="A10" s="53" t="s">
+        <v>1025</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>993</v>
+        <v>1026</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>994</v>
+        <v>1027</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="s">
-        <v>995</v>
+      <c r="A11" s="53" t="s">
+        <v>1028</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>996</v>
+        <v>1029</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>81</v>
@@ -9450,24 +9675,24 @@
         <v>81</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>997</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="s">
-        <v>998</v>
+      <c r="A12" s="53" t="s">
+        <v>1031</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>999</v>
+        <v>1032</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>1000</v>
+        <v>1033</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>81</v>
@@ -9476,50 +9701,50 @@
         <v>81</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1001</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="s">
-        <v>1002</v>
+      <c r="A13" s="53" t="s">
+        <v>1035</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>1003</v>
+        <v>1036</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1004</v>
+        <v>1037</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1005</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="s">
-        <v>1006</v>
+      <c r="A14" s="53" t="s">
+        <v>1039</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>81</v>
@@ -9528,116 +9753,116 @@
         <v>81</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1008</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="s">
-        <v>1009</v>
+      <c r="A15" s="53" t="s">
+        <v>1042</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>1010</v>
+        <v>1043</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="s">
-        <v>1011</v>
+      <c r="A16" s="53" t="s">
+        <v>1044</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1012</v>
+        <v>1045</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1004</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="s">
-        <v>1013</v>
+      <c r="A17" s="53" t="s">
+        <v>1046</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1016</v>
+        <v>1049</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="s">
-        <v>1017</v>
+      <c r="A18" s="53" t="s">
+        <v>1050</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="s">
-        <v>1020</v>
+      <c r="A19" s="53" t="s">
+        <v>1053</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>1021</v>
+        <v>1054</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>81</v>
@@ -9646,47 +9871,47 @@
         <v>81</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1022</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="s">
-        <v>1023</v>
+      <c r="A20" s="53" t="s">
+        <v>1056</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>1024</v>
+        <v>1057</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1012</v>
+        <v>1045</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="s">
-        <v>1025</v>
+      <c r="A21" s="53" t="s">
+        <v>1058</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>81</v>
@@ -9695,50 +9920,50 @@
         <v>81</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1027</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="s">
-        <v>1028</v>
+      <c r="A22" s="53" t="s">
+        <v>1061</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>1029</v>
+        <v>1062</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1004</v>
+        <v>1037</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1030</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="s">
-        <v>1031</v>
+      <c r="A23" s="53" t="s">
+        <v>1064</v>
       </c>
       <c r="B23" s="40" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>81</v>
@@ -9747,21 +9972,21 @@
         <v>81</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="s">
-        <v>1034</v>
+      <c r="A24" s="53" t="s">
+        <v>1067</v>
       </c>
       <c r="B24" s="40" t="s">
         <v>162</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>1035</v>
+        <v>1068</v>
       </c>
       <c r="D24" s="40" t="s">
         <v>47</v>
@@ -9773,21 +9998,21 @@
         <v>72</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>1036</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="s">
-        <v>1037</v>
+      <c r="A25" s="53" t="s">
+        <v>1070</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D25" s="40" t="s">
         <v>47</v>
@@ -9799,35 +10024,35 @@
         <v>357</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1038</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B27" s="49" t="s">
+      <c r="A27" s="50" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B27" s="51" t="s">
         <v>208</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>1040</v>
+        <v>1073</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="s">
-        <v>1041</v>
+      <c r="A28" s="53" t="s">
+        <v>1074</v>
       </c>
       <c r="B28" s="40" t="s">
         <v>218</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>1042</v>
+        <v>1075</v>
       </c>
       <c r="D28" s="40" t="s">
         <v>208</v>
@@ -9839,18 +10064,18 @@
         <v>223</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="51" t="s">
-        <v>1043</v>
+      <c r="A29" s="53" t="s">
+        <v>1076</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>1044</v>
+        <v>1077</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>1045</v>
+        <v>1078</v>
       </c>
       <c r="D29" s="40" t="s">
         <v>218</v>
@@ -9862,18 +10087,18 @@
         <v>261</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>1046</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="s">
-        <v>1047</v>
+      <c r="A30" s="53" t="s">
+        <v>1080</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>1048</v>
+        <v>1081</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>222</v>
@@ -9888,21 +10113,21 @@
         <v>223</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>1049</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="51" t="s">
-        <v>1050</v>
+      <c r="A31" s="53" t="s">
+        <v>1083</v>
       </c>
       <c r="B31" s="40" t="s">
         <v>233</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>1051</v>
+        <v>1084</v>
       </c>
       <c r="D31" s="40" t="s">
         <v>208</v>
@@ -9911,18 +10136,18 @@
         <v>85</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>1052</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="s">
-        <v>1053</v>
+      <c r="A32" s="53" t="s">
+        <v>1086</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>1054</v>
+        <v>1087</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>1055</v>
+        <v>1088</v>
       </c>
       <c r="D32" s="40" t="s">
         <v>233</v>
@@ -9931,18 +10156,18 @@
         <v>85</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1056</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="s">
-        <v>1057</v>
+      <c r="A33" s="53" t="s">
+        <v>1090</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>1058</v>
+        <v>1091</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>1059</v>
+        <v>1092</v>
       </c>
       <c r="D33" s="40" t="s">
         <v>233</v>
@@ -9951,18 +10176,18 @@
         <v>85</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1060</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="s">
-        <v>1061</v>
+      <c r="A34" s="53" t="s">
+        <v>1094</v>
       </c>
       <c r="B34" s="40" t="s">
         <v>236</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>1062</v>
+        <v>1095</v>
       </c>
       <c r="D34" s="40" t="s">
         <v>208</v>
@@ -9971,18 +10196,18 @@
         <v>85</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>1063</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="s">
-        <v>1064</v>
+      <c r="A35" s="53" t="s">
+        <v>1097</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>1065</v>
+        <v>1098</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>1066</v>
+        <v>1099</v>
       </c>
       <c r="D35" s="40" t="s">
         <v>208</v>
@@ -9991,21 +10216,21 @@
         <v>85</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>1067</v>
+        <v>1100</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>1004</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="51" t="s">
-        <v>1068</v>
+      <c r="A36" s="53" t="s">
+        <v>1101</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>1069</v>
+        <v>1102</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>1070</v>
+        <v>1103</v>
       </c>
       <c r="D36" s="40" t="s">
         <v>208</v>
@@ -10017,21 +10242,21 @@
         <v>214</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>1071</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="51" t="s">
-        <v>1072</v>
+      <c r="A37" s="53" t="s">
+        <v>1105</v>
       </c>
       <c r="B37" s="40" t="s">
         <v>225</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>1073</v>
+        <v>1106</v>
       </c>
       <c r="D37" s="40" t="s">
         <v>208</v>
@@ -10040,36 +10265,36 @@
         <v>85</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>1074</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="48" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B39" s="49" t="s">
-        <v>1076</v>
+      <c r="A39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>1109</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D39" s="50"/>
+        <v>1110</v>
+      </c>
+      <c r="D39" s="52"/>
       <c r="E39" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="51" t="s">
-        <v>1078</v>
+      <c r="A40" s="53" t="s">
+        <v>1111</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>1079</v>
+        <v>1112</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>1080</v>
+        <v>1113</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>67</v>
@@ -10078,24 +10303,24 @@
         <v>67</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>1081</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="51" t="s">
-        <v>1082</v>
+      <c r="A41" s="53" t="s">
+        <v>1115</v>
       </c>
       <c r="B41" s="40" t="s">
         <v>133</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>1083</v>
+        <v>1116</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>67</v>
@@ -10104,50 +10329,50 @@
         <v>67</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>1085</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="51" t="s">
-        <v>1086</v>
+      <c r="A42" s="53" t="s">
+        <v>1119</v>
       </c>
       <c r="B42" s="40" t="s">
         <v>100</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>67</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>1088</v>
+        <v>1121</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="51" t="s">
-        <v>1089</v>
+      <c r="A43" s="53" t="s">
+        <v>1122</v>
       </c>
       <c r="B43" s="40" t="s">
         <v>136</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>1090</v>
+        <v>1123</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>67</v>
@@ -10156,24 +10381,24 @@
         <v>67</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>1091</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="51" t="s">
-        <v>1092</v>
+      <c r="A44" s="53" t="s">
+        <v>1125</v>
       </c>
       <c r="B44" s="40" t="s">
         <v>138</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>1093</v>
+        <v>1126</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>67</v>
@@ -10182,24 +10407,24 @@
         <v>117</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>1094</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="51" t="s">
-        <v>1095</v>
+      <c r="A45" s="53" t="s">
+        <v>1128</v>
       </c>
       <c r="B45" s="40" t="s">
         <v>141</v>
       </c>
       <c r="C45" s="40" t="s">
-        <v>1096</v>
+        <v>1129</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>67</v>
@@ -10208,24 +10433,24 @@
         <v>67</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>1097</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="51" t="s">
-        <v>1098</v>
+      <c r="A46" s="53" t="s">
+        <v>1131</v>
       </c>
       <c r="B46" s="40" t="s">
         <v>144</v>
       </c>
       <c r="C46" s="40" t="s">
-        <v>1099</v>
+        <v>1132</v>
       </c>
       <c r="D46" s="40" t="s">
         <v>138</v>
@@ -10237,34 +10462,34 @@
         <v>67</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>1100</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B48" s="52" t="s">
-        <v>1102</v>
+        <v>1134</v>
+      </c>
+      <c r="B48" s="54" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B49" s="52" t="s">
-        <v>1104</v>
+        <v>1136</v>
+      </c>
+      <c r="B49" s="54" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="40" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B50" s="51" t="s">
-        <v>1106</v>
+        <v>1138</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>1139</v>
       </c>
       <c r="C50" s="40"/>
       <c r="D50" s="40"/>
@@ -10277,393 +10502,393 @@
     </row>
     <row r="52">
       <c r="A52" s="40" t="s">
-        <v>1107</v>
+        <v>1140</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>957</v>
+        <v>990</v>
       </c>
       <c r="C52" s="40"/>
       <c r="D52" s="40" t="s">
-        <v>959</v>
+        <v>992</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>958</v>
+        <v>991</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="51" t="s">
-        <v>963</v>
+      <c r="A53" s="53" t="s">
+        <v>996</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>964</v>
-      </c>
-      <c r="C53" s="50"/>
-      <c r="D53" s="50"/>
+        <v>997</v>
+      </c>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
       <c r="E53" s="40" t="s">
-        <v>965</v>
+        <v>998</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="51" t="s">
-        <v>966</v>
+      <c r="A54" s="53" t="s">
+        <v>999</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>967</v>
+        <v>1000</v>
       </c>
       <c r="C54" s="40"/>
       <c r="D54" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>968</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="51" t="s">
-        <v>971</v>
+      <c r="A55" s="53" t="s">
+        <v>1004</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="C55" s="40"/>
       <c r="D55" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="51" t="s">
-        <v>975</v>
+      <c r="A56" s="53" t="s">
+        <v>1008</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="C56" s="40"/>
       <c r="D56" s="40" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>977</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="51" t="s">
-        <v>979</v>
+      <c r="A57" s="53" t="s">
+        <v>1012</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="C57" s="40"/>
       <c r="D57" s="40" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>981</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="51" t="s">
-        <v>983</v>
+      <c r="A58" s="53" t="s">
+        <v>1016</v>
       </c>
       <c r="B58" s="40" t="s">
         <v>311</v>
       </c>
       <c r="C58" s="40"/>
       <c r="D58" s="40" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>984</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="51" t="s">
-        <v>986</v>
+      <c r="A59" s="53" t="s">
+        <v>1019</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="C59" s="40"/>
       <c r="D59" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>988</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="51" t="s">
-        <v>989</v>
+      <c r="A60" s="53" t="s">
+        <v>1022</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C60" s="40"/>
       <c r="D60" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>990</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="51" t="s">
-        <v>992</v>
+      <c r="A61" s="53" t="s">
+        <v>1025</v>
       </c>
       <c r="B61" s="40" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>993</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="51" t="s">
-        <v>995</v>
+      <c r="A62" s="53" t="s">
+        <v>1028</v>
       </c>
       <c r="B62" s="40" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C62" s="40"/>
       <c r="D62" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>996</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="51" t="s">
-        <v>998</v>
+      <c r="A63" s="53" t="s">
+        <v>1031</v>
       </c>
       <c r="B63" s="40" t="s">
-        <v>999</v>
+        <v>1032</v>
       </c>
       <c r="C63" s="40"/>
       <c r="D63" s="40" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>1000</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="51" t="s">
-        <v>1002</v>
+      <c r="A64" s="53" t="s">
+        <v>1035</v>
       </c>
       <c r="B64" s="40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C64" s="40"/>
       <c r="D64" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>1003</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="51" t="s">
-        <v>1006</v>
+      <c r="A65" s="53" t="s">
+        <v>1039</v>
       </c>
       <c r="B65" s="40" t="s">
-        <v>1108</v>
+        <v>1141</v>
       </c>
       <c r="C65" s="40"/>
       <c r="D65" s="40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>1007</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="51" t="s">
-        <v>1009</v>
+      <c r="A66" s="53" t="s">
+        <v>1042</v>
       </c>
       <c r="B66" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C66" s="40"/>
       <c r="D66" s="40" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>1010</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="51" t="s">
-        <v>1011</v>
+      <c r="A67" s="53" t="s">
+        <v>1044</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C67" s="40"/>
       <c r="D67" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="51" t="s">
-        <v>1013</v>
+      <c r="A68" s="53" t="s">
+        <v>1046</v>
       </c>
       <c r="B68" s="40" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="C68" s="40"/>
       <c r="D68" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="51" t="s">
-        <v>1017</v>
+      <c r="A69" s="53" t="s">
+        <v>1050</v>
       </c>
       <c r="B69" s="40" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C69" s="40"/>
       <c r="D69" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="51" t="s">
-        <v>1020</v>
+      <c r="A70" s="53" t="s">
+        <v>1053</v>
       </c>
       <c r="B70" s="40" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C70" s="40"/>
       <c r="D70" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E70" s="40" t="s">
-        <v>1021</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="51" t="s">
-        <v>1023</v>
+      <c r="A71" s="53" t="s">
+        <v>1056</v>
       </c>
       <c r="B71" s="40" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C71" s="40"/>
       <c r="D71" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>1024</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="51" t="s">
-        <v>1025</v>
+      <c r="A72" s="53" t="s">
+        <v>1058</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C72" s="40"/>
       <c r="D72" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="51" t="s">
-        <v>1028</v>
+      <c r="A73" s="53" t="s">
+        <v>1061</v>
       </c>
       <c r="B73" s="40" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C73" s="40"/>
       <c r="D73" s="40" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>1029</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="51" t="s">
-        <v>1031</v>
+      <c r="A74" s="53" t="s">
+        <v>1064</v>
       </c>
       <c r="B74" s="40" t="s">
         <v>47</v>
       </c>
       <c r="C74" s="40"/>
       <c r="D74" s="40" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="51" t="s">
-        <v>1034</v>
+      <c r="A75" s="53" t="s">
+        <v>1067</v>
       </c>
       <c r="B75" s="40" t="s">
-        <v>1109</v>
+        <v>1142</v>
       </c>
       <c r="C75" s="40"/>
       <c r="D75" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>1035</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="51" t="s">
-        <v>1037</v>
+      <c r="A76" s="53" t="s">
+        <v>1070</v>
       </c>
       <c r="B76" s="40" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C76" s="40"/>
       <c r="D76" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="51" t="s">
-        <v>1039</v>
+      <c r="A77" s="53" t="s">
+        <v>1072</v>
       </c>
       <c r="B77" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="C77" s="50"/>
-      <c r="D77" s="50"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
       <c r="E77" s="40" t="s">
-        <v>1040</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="51" t="s">
-        <v>1041</v>
+      <c r="A78" s="53" t="s">
+        <v>1074</v>
       </c>
       <c r="B78" s="40" t="s">
         <v>218</v>
@@ -10673,30 +10898,30 @@
         <v>208</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>1042</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="51" t="s">
-        <v>1043</v>
+      <c r="A79" s="53" t="s">
+        <v>1076</v>
       </c>
       <c r="B79" s="40" t="s">
-        <v>1110</v>
+        <v>1143</v>
       </c>
       <c r="C79" s="40"/>
       <c r="D79" s="40" t="s">
         <v>218</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>1045</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="51" t="s">
-        <v>1047</v>
+      <c r="A80" s="53" t="s">
+        <v>1080</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>1048</v>
+        <v>1081</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="40" t="s">
@@ -10707,8 +10932,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="51" t="s">
-        <v>1050</v>
+      <c r="A81" s="53" t="s">
+        <v>1083</v>
       </c>
       <c r="B81" s="40" t="s">
         <v>233</v>
@@ -10718,42 +10943,42 @@
         <v>208</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>1051</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="51" t="s">
-        <v>1053</v>
+      <c r="A82" s="53" t="s">
+        <v>1086</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>1054</v>
+        <v>1087</v>
       </c>
       <c r="C82" s="40"/>
       <c r="D82" s="40" t="s">
         <v>233</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>1055</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="51" t="s">
-        <v>1057</v>
+      <c r="A83" s="53" t="s">
+        <v>1090</v>
       </c>
       <c r="B83" s="40" t="s">
-        <v>1058</v>
+        <v>1091</v>
       </c>
       <c r="C83" s="40"/>
       <c r="D83" s="40" t="s">
         <v>233</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>1059</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="51" t="s">
-        <v>1061</v>
+      <c r="A84" s="53" t="s">
+        <v>1094</v>
       </c>
       <c r="B84" s="40" t="s">
         <v>236</v>
@@ -10763,42 +10988,42 @@
         <v>208</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>1062</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="51" t="s">
-        <v>1064</v>
+      <c r="A85" s="53" t="s">
+        <v>1097</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>1065</v>
+        <v>1098</v>
       </c>
       <c r="C85" s="40"/>
       <c r="D85" s="40" t="s">
         <v>208</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>1066</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="51" t="s">
-        <v>1068</v>
+      <c r="A86" s="53" t="s">
+        <v>1101</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>1111</v>
+        <v>1144</v>
       </c>
       <c r="C86" s="40"/>
       <c r="D86" s="40" t="s">
         <v>208</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>1070</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="51" t="s">
-        <v>1072</v>
+      <c r="A87" s="53" t="s">
+        <v>1105</v>
       </c>
       <c r="B87" s="40" t="s">
         <v>225</v>
@@ -10808,115 +11033,115 @@
         <v>208</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>1073</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="51" t="s">
-        <v>1075</v>
+      <c r="A88" s="53" t="s">
+        <v>1108</v>
       </c>
       <c r="B88" s="40" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C88" s="50"/>
-      <c r="D88" s="50"/>
+        <v>1109</v>
+      </c>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
       <c r="E88" s="40" t="s">
-        <v>1077</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="51" t="s">
-        <v>1078</v>
+      <c r="A89" s="53" t="s">
+        <v>1111</v>
       </c>
       <c r="B89" s="40" t="s">
-        <v>1079</v>
+        <v>1112</v>
       </c>
       <c r="C89" s="40"/>
       <c r="D89" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>1080</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="51" t="s">
-        <v>1082</v>
+      <c r="A90" s="53" t="s">
+        <v>1115</v>
       </c>
       <c r="B90" s="40" t="s">
         <v>133</v>
       </c>
       <c r="C90" s="40"/>
       <c r="D90" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>1083</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="51" t="s">
-        <v>1086</v>
+      <c r="A91" s="53" t="s">
+        <v>1119</v>
       </c>
       <c r="B91" s="40" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="40"/>
       <c r="D91" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="51" t="s">
-        <v>1089</v>
+      <c r="A92" s="53" t="s">
+        <v>1122</v>
       </c>
       <c r="B92" s="40" t="s">
         <v>136</v>
       </c>
       <c r="C92" s="40"/>
       <c r="D92" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>1090</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="51" t="s">
-        <v>1092</v>
+      <c r="A93" s="53" t="s">
+        <v>1125</v>
       </c>
       <c r="B93" s="40" t="s">
         <v>138</v>
       </c>
       <c r="C93" s="40"/>
       <c r="D93" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>1093</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="51" t="s">
-        <v>1095</v>
+      <c r="A94" s="53" t="s">
+        <v>1128</v>
       </c>
       <c r="B94" s="40" t="s">
         <v>141</v>
       </c>
       <c r="C94" s="40"/>
       <c r="D94" s="40" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>1096</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="51" t="s">
-        <v>1098</v>
+      <c r="A95" s="53" t="s">
+        <v>1131</v>
       </c>
       <c r="B95" s="40" t="s">
         <v>144</v>
@@ -10926,7 +11151,7 @@
         <v>138</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>1099</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -15543,10 +15768,10 @@
       <c r="B11" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="27" t="s">
         <v>357</v>
       </c>
       <c r="E11" s="26" t="s">
@@ -15558,14 +15783,14 @@
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="28">
-        <v>45627.0</v>
+        <v>46062.0</v>
       </c>
       <c r="L11" s="26"/>
       <c r="M11" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="26" t="s">
-        <v>22</v>
+      <c r="N11" s="27" t="s">
+        <v>50</v>
       </c>
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
@@ -15593,7 +15818,7 @@
       <c r="B12" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="26" t="s">
         <v>360</v>
       </c>
       <c r="D12" s="26" t="s">
@@ -15647,7 +15872,7 @@
         <v>363</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>81</v>
@@ -15688,16 +15913,16 @@
     </row>
     <row r="14">
       <c r="A14" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="C14" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="D14" s="26" t="s">
         <v>367</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>364</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>81</v>
@@ -15706,9 +15931,7 @@
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="30" t="s">
-        <v>368</v>
-      </c>
+      <c r="J14" s="26"/>
       <c r="K14" s="28">
         <v>45627.0</v>
       </c>
@@ -15740,16 +15963,16 @@
     </row>
     <row r="15">
       <c r="A15" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>369</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="C15" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="D15" s="27" t="s">
         <v>371</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>372</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>81</v>
@@ -15758,7 +15981,9 @@
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="J15" s="30" t="s">
+        <v>372</v>
+      </c>
       <c r="K15" s="28">
         <v>45627.0</v>
       </c>
@@ -15799,7 +16024,7 @@
         <v>375</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>81</v>
@@ -15816,8 +16041,8 @@
       <c r="M16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="27" t="s">
-        <v>45</v>
+      <c r="N16" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="O16" s="26"/>
       <c r="P16" s="26"/>
@@ -15840,16 +16065,16 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>376</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>372</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>81</v>
@@ -15866,8 +16091,8 @@
       <c r="M17" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N17" s="26" t="s">
-        <v>22</v>
+      <c r="N17" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="O17" s="26"/>
       <c r="P17" s="26"/>
@@ -15890,16 +16115,16 @@
     </row>
     <row r="18">
       <c r="A18" s="27" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>81</v>
@@ -15916,8 +16141,8 @@
       <c r="M18" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="27" t="s">
-        <v>45</v>
+      <c r="N18" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="O18" s="26"/>
       <c r="P18" s="26"/>
@@ -15940,16 +16165,16 @@
     </row>
     <row r="19">
       <c r="A19" s="27" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>81</v>
@@ -15958,9 +16183,7 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="27" t="s">
-        <v>385</v>
-      </c>
+      <c r="J19" s="26"/>
       <c r="K19" s="28">
         <v>45627.0</v>
       </c>
@@ -15968,8 +16191,8 @@
       <c r="M19" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N19" s="26" t="s">
-        <v>22</v>
+      <c r="N19" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="O19" s="26"/>
       <c r="P19" s="26"/>
@@ -16001,7 +16224,7 @@
         <v>388</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>81</v>
@@ -16010,7 +16233,9 @@
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="J20" s="27" t="s">
+        <v>389</v>
+      </c>
       <c r="K20" s="28">
         <v>45627.0</v>
       </c>
@@ -16051,7 +16276,7 @@
         <v>392</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>81</v>
@@ -16092,16 +16317,16 @@
     </row>
     <row r="22">
       <c r="A22" s="27" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>81</v>
@@ -16142,7 +16367,7 @@
     </row>
     <row r="23">
       <c r="A23" s="27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>397</v>
@@ -16151,7 +16376,7 @@
         <v>398</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>81</v>
@@ -16192,13 +16417,13 @@
     </row>
     <row r="24">
       <c r="A24" s="27" t="s">
-        <v>399</v>
-      </c>
-      <c r="B24" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="B24" s="27" t="s">
         <v>401</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>402</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>357</v>
@@ -16210,18 +16435,16 @@
       <c r="G24" s="26"/>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="27" t="s">
-        <v>49</v>
-      </c>
+      <c r="J24" s="26"/>
       <c r="K24" s="28">
-        <v>46008.0</v>
+        <v>45627.0</v>
       </c>
       <c r="L24" s="26"/>
       <c r="M24" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N24" s="27" t="s">
-        <v>50</v>
+      <c r="N24" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="O24" s="26"/>
       <c r="P24" s="26"/>
@@ -16243,20 +16466,38 @@
       <c r="AF24" s="26"/>
     </row>
     <row r="25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="A25" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>81</v>
+      </c>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="28"/>
+      <c r="J25" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="28">
+        <v>46008.0</v>
+      </c>
       <c r="L25" s="26"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="26"/>
+      <c r="M25" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="27" t="s">
+        <v>50</v>
+      </c>
       <c r="O25" s="26"/>
       <c r="P25" s="26"/>
       <c r="Q25" s="26"/>
@@ -16277,36 +16518,20 @@
       <c r="AF25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>404</v>
-      </c>
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="26" t="s">
-        <v>81</v>
-      </c>
+      <c r="E26" s="26"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
-      <c r="J26" s="27" t="s">
-        <v>405</v>
-      </c>
-      <c r="K26" s="28">
-        <v>45627.0</v>
-      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="26"/>
-      <c r="M26" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="26" t="s">
-        <v>22</v>
-      </c>
+      <c r="M26" s="27"/>
+      <c r="N26" s="26"/>
       <c r="O26" s="26"/>
       <c r="P26" s="26"/>
       <c r="Q26" s="26"/>
@@ -16327,18 +16552,16 @@
       <c r="AF26" s="26"/>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="37" t="s">
         <v>406</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>409</v>
-      </c>
+      <c r="D27" s="26"/>
       <c r="E27" s="26" t="s">
         <v>81</v>
       </c>
@@ -16346,8 +16569,8 @@
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
-      <c r="J27" s="26" t="s">
-        <v>106</v>
+      <c r="J27" s="27" t="s">
+        <v>409</v>
       </c>
       <c r="K27" s="28">
         <v>45627.0</v>
@@ -16389,7 +16612,7 @@
         <v>412</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E28" s="26" t="s">
         <v>81</v>
@@ -16397,11 +16620,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
-      <c r="I28" s="27" t="s">
-        <v>413</v>
-      </c>
-      <c r="J28" s="27" t="s">
-        <v>414</v>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26" t="s">
+        <v>106</v>
       </c>
       <c r="K28" s="28">
         <v>45627.0</v>
@@ -16434,16 +16655,16 @@
     </row>
     <row r="29">
       <c r="A29" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="B29" s="27" t="s">
         <v>415</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="C29" s="27" t="s">
         <v>416</v>
       </c>
-      <c r="C29" s="27" t="s">
-        <v>417</v>
-      </c>
       <c r="D29" s="26" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>81</v>
@@ -16451,9 +16672,11 @@
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26" t="s">
-        <v>106</v>
+      <c r="I29" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="J29" s="27" t="s">
+        <v>418</v>
       </c>
       <c r="K29" s="28">
         <v>45627.0</v>
@@ -16486,16 +16709,16 @@
     </row>
     <row r="30">
       <c r="A30" s="27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>81</v>
@@ -16540,14 +16763,14 @@
       <c r="A31" s="27" t="s">
         <v>422</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="27" t="s">
         <v>423</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="27" t="s">
         <v>424</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>81</v>
@@ -16556,18 +16779,18 @@
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="27" t="s">
-        <v>49</v>
+      <c r="J31" s="26" t="s">
+        <v>106</v>
       </c>
       <c r="K31" s="28">
-        <v>46008.0</v>
+        <v>45627.0</v>
       </c>
       <c r="L31" s="26"/>
       <c r="M31" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N31" s="27" t="s">
-        <v>50</v>
+      <c r="N31" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="O31" s="26"/>
       <c r="P31" s="26"/>
@@ -16590,16 +16813,16 @@
     </row>
     <row r="32">
       <c r="A32" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="D32" s="26" t="s">
         <v>425</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>426</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>427</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>421</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>81</v>
@@ -16609,17 +16832,17 @@
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
       <c r="J32" s="27" t="s">
-        <v>428</v>
+        <v>49</v>
       </c>
       <c r="K32" s="28">
-        <v>45627.0</v>
+        <v>46008.0</v>
       </c>
       <c r="L32" s="26"/>
       <c r="M32" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N32" s="26" t="s">
-        <v>22</v>
+      <c r="N32" s="27" t="s">
+        <v>50</v>
       </c>
       <c r="O32" s="26"/>
       <c r="P32" s="26"/>
@@ -16644,14 +16867,14 @@
       <c r="A33" s="27" t="s">
         <v>429</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="27" t="s">
         <v>430</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>431</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>81</v>
@@ -16661,17 +16884,17 @@
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
       <c r="J33" s="27" t="s">
-        <v>49</v>
+        <v>432</v>
       </c>
       <c r="K33" s="28">
-        <v>46008.0</v>
+        <v>45627.0</v>
       </c>
       <c r="L33" s="26"/>
       <c r="M33" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N33" s="27" t="s">
-        <v>50</v>
+      <c r="N33" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="O33" s="26"/>
       <c r="P33" s="26"/>
@@ -16694,16 +16917,16 @@
     </row>
     <row r="34">
       <c r="A34" s="27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="D34" s="27" t="s">
         <v>435</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>425</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>81</v>
@@ -16754,8 +16977,8 @@
       <c r="C35" s="27" t="s">
         <v>438</v>
       </c>
-      <c r="D35" s="26" t="s">
-        <v>421</v>
+      <c r="D35" s="27" t="s">
+        <v>439</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>81</v>
@@ -16798,16 +17021,16 @@
     </row>
     <row r="36">
       <c r="A36" s="27" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>81</v>
@@ -16850,16 +17073,16 @@
     </row>
     <row r="37">
       <c r="A37" s="27" t="s">
-        <v>442</v>
-      </c>
-      <c r="B37" s="35" t="s">
         <v>443</v>
       </c>
+      <c r="B37" s="26" t="s">
+        <v>444</v>
+      </c>
       <c r="C37" s="27" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>81</v>
@@ -16902,16 +17125,16 @@
     </row>
     <row r="38">
       <c r="A38" s="27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>81</v>
@@ -16953,20 +17176,38 @@
       <c r="AF38" s="26"/>
     </row>
     <row r="39">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
+      <c r="A39" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>450</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>425</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>81</v>
+      </c>
       <c r="F39" s="26"/>
       <c r="G39" s="26"/>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="28"/>
+      <c r="J39" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" s="28">
+        <v>46008.0</v>
+      </c>
       <c r="L39" s="26"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="26"/>
+      <c r="M39" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="27" t="s">
+        <v>50</v>
+      </c>
       <c r="O39" s="26"/>
       <c r="P39" s="26"/>
       <c r="Q39" s="26"/>
@@ -16987,36 +17228,20 @@
       <c r="AF39" s="26"/>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="s">
-        <v>448</v>
-      </c>
-      <c r="B40" s="37" t="s">
-        <v>449</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>450</v>
-      </c>
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="27"/>
       <c r="D40" s="26"/>
-      <c r="E40" s="26" t="s">
-        <v>81</v>
-      </c>
+      <c r="E40" s="26"/>
       <c r="F40" s="26"/>
       <c r="G40" s="26"/>
       <c r="H40" s="26"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="27" t="s">
-        <v>451</v>
-      </c>
-      <c r="K40" s="28">
-        <v>45627.0</v>
-      </c>
+      <c r="J40" s="27"/>
+      <c r="K40" s="28"/>
       <c r="L40" s="26"/>
-      <c r="M40" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="N40" s="26" t="s">
-        <v>22</v>
-      </c>
+      <c r="M40" s="27"/>
+      <c r="N40" s="26"/>
       <c r="O40" s="26"/>
       <c r="P40" s="26"/>
       <c r="Q40" s="26"/>
@@ -17037,18 +17262,16 @@
       <c r="AF40" s="26"/>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="37" t="s">
         <v>453</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>454</v>
       </c>
-      <c r="D41" s="26" t="s">
-        <v>455</v>
-      </c>
+      <c r="D41" s="26"/>
       <c r="E41" s="26" t="s">
         <v>81</v>
       </c>
@@ -17056,8 +17279,8 @@
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
-      <c r="J41" s="26" t="s">
-        <v>106</v>
+      <c r="J41" s="27" t="s">
+        <v>455</v>
       </c>
       <c r="K41" s="28">
         <v>45627.0</v>
@@ -17089,67 +17312,69 @@
       <c r="AF41" s="26"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="27" t="s">
         <v>456</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="27" t="s">
         <v>457</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="27" t="s">
         <v>458</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26" t="s">
+        <v>106</v>
+      </c>
       <c r="K42" s="28">
         <v>45627.0</v>
       </c>
-      <c r="L42" s="7"/>
+      <c r="L42" s="26"/>
       <c r="M42" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N42" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="7"/>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="7"/>
-      <c r="AC42" s="7"/>
-      <c r="AD42" s="7"/>
-      <c r="AE42" s="7"/>
-      <c r="AF42" s="7"/>
+      <c r="N42" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="26"/>
+      <c r="W42" s="26"/>
+      <c r="X42" s="26"/>
+      <c r="Y42" s="26"/>
+      <c r="Z42" s="26"/>
+      <c r="AA42" s="26"/>
+      <c r="AB42" s="26"/>
+      <c r="AC42" s="26"/>
+      <c r="AD42" s="26"/>
+      <c r="AE42" s="26"/>
+      <c r="AF42" s="26"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D43" s="26" t="s">
         <v>459</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>455</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>81</v>
@@ -17190,16 +17415,16 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>81</v>
@@ -17239,70 +17464,70 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45">
-      <c r="K45" s="28"/>
-      <c r="M45" s="27"/>
+      <c r="A45" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>459</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="28">
+        <v>45627.0</v>
+      </c>
+      <c r="L45" s="7"/>
+      <c r="M45" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N45" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="7"/>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
+      <c r="AC45" s="7"/>
+      <c r="AD45" s="7"/>
+      <c r="AE45" s="7"/>
+      <c r="AF45" s="7"/>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="s">
-        <v>465</v>
-      </c>
-      <c r="B46" s="37" t="s">
-        <v>466</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>467</v>
-      </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="28">
-        <v>45627.0</v>
-      </c>
-      <c r="L46" s="26"/>
-      <c r="M46" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="N46" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="O46" s="26"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="26"/>
-      <c r="R46" s="26"/>
-      <c r="S46" s="26"/>
-      <c r="T46" s="26"/>
-      <c r="U46" s="26"/>
-      <c r="V46" s="26"/>
-      <c r="W46" s="26"/>
-      <c r="X46" s="26"/>
-      <c r="Y46" s="26"/>
-      <c r="Z46" s="26"/>
-      <c r="AA46" s="26"/>
-      <c r="AB46" s="26"/>
-      <c r="AC46" s="26"/>
-      <c r="AD46" s="26"/>
-      <c r="AE46" s="26"/>
-      <c r="AF46" s="26"/>
+      <c r="K46" s="28"/>
+      <c r="M46" s="27"/>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="B47" s="27" t="s">
+      <c r="A47" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="B47" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="D47" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>471</v>
       </c>
+      <c r="D47" s="26"/>
       <c r="E47" s="26" t="s">
         <v>81</v>
       </c>
@@ -17310,9 +17535,7 @@
       <c r="G47" s="26"/>
       <c r="H47" s="26"/>
       <c r="I47" s="26"/>
-      <c r="J47" s="27" t="s">
-        <v>472</v>
-      </c>
+      <c r="J47" s="26"/>
       <c r="K47" s="28">
         <v>45627.0</v>
       </c>
@@ -17320,8 +17543,8 @@
       <c r="M47" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N47" s="26" t="s">
-        <v>22</v>
+      <c r="N47" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="O47" s="26"/>
       <c r="P47" s="26"/>
@@ -17344,16 +17567,16 @@
     </row>
     <row r="48">
       <c r="A48" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="B48" s="27" t="s">
         <v>473</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="C48" s="27" t="s">
         <v>474</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="D48" s="26" t="s">
         <v>475</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>471</v>
       </c>
       <c r="E48" s="26" t="s">
         <v>81</v>
@@ -17401,11 +17624,11 @@
       <c r="B49" s="27" t="s">
         <v>478</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="27" t="s">
         <v>479</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>81</v>
@@ -17453,11 +17676,11 @@
       <c r="B50" s="27" t="s">
         <v>482</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" s="26" t="s">
         <v>483</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E50" s="26" t="s">
         <v>81</v>
@@ -17509,7 +17732,7 @@
         <v>487</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>81</v>
@@ -17561,7 +17784,7 @@
         <v>491</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E52" s="26" t="s">
         <v>81</v>
@@ -17613,7 +17836,7 @@
         <v>495</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="E53" s="26" t="s">
         <v>81</v>
@@ -17623,7 +17846,7 @@
       <c r="H53" s="26"/>
       <c r="I53" s="26"/>
       <c r="J53" s="27" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K53" s="28">
         <v>45627.0</v>
@@ -17656,16 +17879,16 @@
     </row>
     <row r="54">
       <c r="A54" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="B54" s="27" t="s">
         <v>498</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="C54" s="27" t="s">
         <v>499</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="D54" s="26" t="s">
         <v>500</v>
-      </c>
-      <c r="D54" s="26" t="s">
-        <v>501</v>
       </c>
       <c r="E54" s="26" t="s">
         <v>81</v>
@@ -17675,7 +17898,7 @@
       <c r="H54" s="26"/>
       <c r="I54" s="26"/>
       <c r="J54" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K54" s="28">
         <v>45627.0</v>
@@ -17708,16 +17931,16 @@
     </row>
     <row r="55">
       <c r="A55" s="27" t="s">
+        <v>502</v>
+      </c>
+      <c r="B55" s="27" t="s">
         <v>503</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="C55" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="C55" s="27" t="s">
-        <v>500</v>
-      </c>
       <c r="D55" s="26" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="E55" s="26" t="s">
         <v>81</v>
@@ -17727,7 +17950,7 @@
       <c r="H55" s="26"/>
       <c r="I55" s="26"/>
       <c r="J55" s="27" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="K55" s="28">
         <v>45627.0</v>
@@ -17759,69 +17982,69 @@
       <c r="AF55" s="26"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="A56" s="27" t="s">
         <v>507</v>
       </c>
+      <c r="B56" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>504</v>
+      </c>
       <c r="D56" s="26" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E56" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="6" t="s">
-        <v>49</v>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="27" t="s">
+        <v>492</v>
       </c>
       <c r="K56" s="28">
-        <v>46008.0</v>
-      </c>
-      <c r="L56" s="7"/>
+        <v>45627.0</v>
+      </c>
+      <c r="L56" s="26"/>
       <c r="M56" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="N56" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O56" s="7"/>
-      <c r="P56" s="7"/>
-      <c r="Q56" s="7"/>
-      <c r="R56" s="7"/>
-      <c r="S56" s="7"/>
-      <c r="T56" s="7"/>
-      <c r="U56" s="7"/>
-      <c r="V56" s="7"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="7"/>
-      <c r="Y56" s="7"/>
-      <c r="Z56" s="7"/>
-      <c r="AA56" s="7"/>
-      <c r="AB56" s="7"/>
-      <c r="AC56" s="7"/>
-      <c r="AD56" s="7"/>
-      <c r="AE56" s="7"/>
-      <c r="AF56" s="7"/>
+      <c r="N56" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O56" s="26"/>
+      <c r="P56" s="26"/>
+      <c r="Q56" s="26"/>
+      <c r="R56" s="26"/>
+      <c r="S56" s="26"/>
+      <c r="T56" s="26"/>
+      <c r="U56" s="26"/>
+      <c r="V56" s="26"/>
+      <c r="W56" s="26"/>
+      <c r="X56" s="26"/>
+      <c r="Y56" s="26"/>
+      <c r="Z56" s="26"/>
+      <c r="AA56" s="26"/>
+      <c r="AB56" s="26"/>
+      <c r="AC56" s="26"/>
+      <c r="AD56" s="26"/>
+      <c r="AE56" s="26"/>
+      <c r="AF56" s="26"/>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="s">
-        <v>508</v>
-      </c>
-      <c r="B57" s="26" t="s">
+      <c r="A57" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="B57" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="C57" s="6" t="s">
         <v>511</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>475</v>
       </c>
       <c r="E57" s="26" t="s">
         <v>81</v>
@@ -17873,7 +18096,7 @@
         <v>514</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E58" s="26" t="s">
         <v>81</v>
@@ -17916,16 +18139,16 @@
     </row>
     <row r="59">
       <c r="A59" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>517</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>515</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>516</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>517</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>511</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>81</v>
@@ -17967,70 +18190,72 @@
       <c r="AF59" s="7"/>
     </row>
     <row r="60">
-      <c r="K60" s="28"/>
-      <c r="M60" s="27"/>
+      <c r="A60" s="27" t="s">
+        <v>519</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K60" s="28">
+        <v>46008.0</v>
+      </c>
+      <c r="L60" s="7"/>
+      <c r="M60" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="W60" s="7"/>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="7"/>
+      <c r="AB60" s="7"/>
+      <c r="AC60" s="7"/>
+      <c r="AD60" s="7"/>
+      <c r="AE60" s="7"/>
+      <c r="AF60" s="7"/>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="s">
-        <v>518</v>
-      </c>
-      <c r="B61" s="37" t="s">
-        <v>519</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>520</v>
-      </c>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="28">
-        <v>45627.0</v>
-      </c>
-      <c r="L61" s="26"/>
-      <c r="M61" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="26"/>
-      <c r="S61" s="26"/>
-      <c r="T61" s="26"/>
-      <c r="U61" s="26"/>
-      <c r="V61" s="26"/>
-      <c r="W61" s="26"/>
-      <c r="X61" s="26"/>
-      <c r="Y61" s="26"/>
-      <c r="Z61" s="26"/>
-      <c r="AA61" s="26"/>
-      <c r="AB61" s="26"/>
-      <c r="AC61" s="26"/>
-      <c r="AD61" s="26"/>
-      <c r="AE61" s="26"/>
-      <c r="AF61" s="26"/>
+      <c r="K61" s="28"/>
+      <c r="M61" s="27"/>
     </row>
     <row r="62">
-      <c r="A62" s="27" t="s">
-        <v>521</v>
-      </c>
-      <c r="B62" s="27" t="s">
+      <c r="A62" s="37" t="s">
         <v>522</v>
       </c>
+      <c r="B62" s="37" t="s">
+        <v>523</v>
+      </c>
       <c r="C62" s="27" t="s">
-        <v>523</v>
-      </c>
-      <c r="D62" s="26" t="s">
         <v>524</v>
       </c>
+      <c r="D62" s="26"/>
       <c r="E62" s="26" t="s">
         <v>81</v>
       </c>
@@ -18129,7 +18354,7 @@
         <v>531</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E64" s="26" t="s">
         <v>81</v>
@@ -18169,20 +18394,36 @@
       <c r="AF64" s="26"/>
     </row>
     <row r="65">
-      <c r="A65" s="26"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
+      <c r="A65" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>534</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>535</v>
+      </c>
+      <c r="D65" s="26" t="s">
+        <v>532</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>81</v>
+      </c>
       <c r="F65" s="26"/>
       <c r="G65" s="26"/>
       <c r="H65" s="26"/>
       <c r="I65" s="26"/>
       <c r="J65" s="26"/>
-      <c r="K65" s="26"/>
+      <c r="K65" s="28">
+        <v>45627.0</v>
+      </c>
       <c r="L65" s="26"/>
-      <c r="M65" s="26"/>
-      <c r="N65" s="26"/>
+      <c r="M65" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N65" s="27" t="s">
+        <v>50</v>
+      </c>
       <c r="O65" s="26"/>
       <c r="P65" s="26"/>
       <c r="Q65" s="26"/>
@@ -18203,12 +18444,8 @@
       <c r="AF65" s="26"/>
     </row>
     <row r="66">
-      <c r="A66" s="37" t="s">
-        <v>532</v>
-      </c>
-      <c r="B66" s="37" t="s">
-        <v>532</v>
-      </c>
+      <c r="A66" s="26"/>
+      <c r="B66" s="26"/>
       <c r="C66" s="26"/>
       <c r="D66" s="26"/>
       <c r="E66" s="26"/>
@@ -18241,19 +18478,15 @@
       <c r="AF66" s="26"/>
     </row>
     <row r="67">
-      <c r="A67" s="27" t="s">
-        <v>533</v>
-      </c>
-      <c r="B67" s="27" t="s">
-        <v>534</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>535</v>
-      </c>
+      <c r="A67" s="37" t="s">
+        <v>536</v>
+      </c>
+      <c r="B67" s="37" t="s">
+        <v>536</v>
+      </c>
+      <c r="C67" s="26"/>
       <c r="D67" s="26"/>
-      <c r="E67" s="26" t="s">
-        <v>81</v>
-      </c>
+      <c r="E67" s="26"/>
       <c r="F67" s="26"/>
       <c r="G67" s="26"/>
       <c r="H67" s="26"/>
@@ -18262,9 +18495,7 @@
       <c r="K67" s="26"/>
       <c r="L67" s="26"/>
       <c r="M67" s="26"/>
-      <c r="N67" s="26" t="s">
-        <v>22</v>
-      </c>
+      <c r="N67" s="26"/>
       <c r="O67" s="26"/>
       <c r="P67" s="26"/>
       <c r="Q67" s="26"/>
@@ -18284,63 +18515,63 @@
       <c r="AE67" s="26"/>
       <c r="AF67" s="26"/>
     </row>
-    <row r="69">
-      <c r="A69" s="37" t="s">
-        <v>536</v>
-      </c>
-      <c r="B69" s="27"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="26"/>
-      <c r="L69" s="26"/>
-      <c r="M69" s="26"/>
-      <c r="N69" s="26"/>
-      <c r="O69" s="26"/>
-      <c r="P69" s="26"/>
-      <c r="Q69" s="26"/>
-      <c r="R69" s="26"/>
-      <c r="S69" s="26"/>
-      <c r="T69" s="26"/>
-      <c r="U69" s="26"/>
-      <c r="V69" s="26"/>
-      <c r="W69" s="26"/>
-      <c r="X69" s="26"/>
-      <c r="Y69" s="26"/>
-      <c r="Z69" s="26"/>
-      <c r="AA69" s="26"/>
-      <c r="AB69" s="26"/>
-      <c r="AC69" s="26"/>
-      <c r="AD69" s="26"/>
-      <c r="AE69" s="26"/>
-      <c r="AF69" s="26"/>
+    <row r="68">
+      <c r="A68" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
+      <c r="N68" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O68" s="26"/>
+      <c r="P68" s="26"/>
+      <c r="Q68" s="26"/>
+      <c r="R68" s="26"/>
+      <c r="S68" s="26"/>
+      <c r="T68" s="26"/>
+      <c r="U68" s="26"/>
+      <c r="V68" s="26"/>
+      <c r="W68" s="26"/>
+      <c r="X68" s="26"/>
+      <c r="Y68" s="26"/>
+      <c r="Z68" s="26"/>
+      <c r="AA68" s="26"/>
+      <c r="AB68" s="26"/>
+      <c r="AC68" s="26"/>
+      <c r="AD68" s="26"/>
+      <c r="AE68" s="26"/>
+      <c r="AF68" s="26"/>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="s">
-        <v>537</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>538</v>
-      </c>
+      <c r="A70" s="37" t="s">
+        <v>540</v>
+      </c>
+      <c r="B70" s="27"/>
       <c r="C70" s="26"/>
-      <c r="D70" s="27" t="s">
-        <v>539</v>
-      </c>
-      <c r="E70" s="27" t="s">
-        <v>81</v>
-      </c>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
       <c r="F70" s="26"/>
       <c r="G70" s="26"/>
       <c r="H70" s="26"/>
       <c r="I70" s="26"/>
-      <c r="J70" s="27" t="s">
-        <v>540</v>
-      </c>
+      <c r="J70" s="26"/>
       <c r="K70" s="26"/>
       <c r="L70" s="26"/>
       <c r="M70" s="26"/>
@@ -18365,103 +18596,130 @@
       <c r="AF70" s="26"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>423</v>
-      </c>
+      <c r="A71" s="27" t="s">
+        <v>541</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>542</v>
+      </c>
+      <c r="C71" s="26"/>
       <c r="D71" s="27" t="s">
-        <v>421</v>
+        <v>543</v>
       </c>
       <c r="E71" s="27" t="s">
         <v>81</v>
       </c>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
       <c r="J71" s="27" t="s">
-        <v>540</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="26"/>
+      <c r="S71" s="26"/>
+      <c r="T71" s="26"/>
+      <c r="U71" s="26"/>
+      <c r="V71" s="26"/>
+      <c r="W71" s="26"/>
+      <c r="X71" s="26"/>
+      <c r="Y71" s="26"/>
+      <c r="Z71" s="26"/>
+      <c r="AA71" s="26"/>
+      <c r="AB71" s="26"/>
+      <c r="AC71" s="26"/>
+      <c r="AD71" s="26"/>
+      <c r="AE71" s="26"/>
+      <c r="AF71" s="26"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>541</v>
+        <v>426</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>542</v>
+        <v>427</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E72" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J72" s="27" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>445</v>
+        <v>545</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>446</v>
+        <v>546</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E73" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J73" s="27" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="J74" s="27"/>
+      <c r="A74" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J74" s="27" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="D75" s="27" t="s">
-        <v>421</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J75" s="27" t="s">
-        <v>540</v>
-      </c>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="J75" s="27"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>334</v>
+        <v>548</v>
+      </c>
+      <c r="D76" s="27" t="s">
+        <v>425</v>
       </c>
       <c r="E76" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J76" s="27" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>334</v>
@@ -18470,558 +18728,575 @@
         <v>81</v>
       </c>
       <c r="J77" s="27" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>551</v>
+        <v>334</v>
       </c>
       <c r="E78" s="27" t="s">
         <v>81</v>
       </c>
+      <c r="J78" s="27" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="27"/>
-      <c r="J79" s="6"/>
+      <c r="A79" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="E80" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>540</v>
-      </c>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="27"/>
+      <c r="J80" s="6"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>552</v>
+        <v>516</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="D81" s="6"/>
+        <v>517</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>81</v>
+      </c>
       <c r="J81" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
+      <c r="A82" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>557</v>
+      </c>
       <c r="D82" s="6"/>
+      <c r="J82" s="6" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="D83" s="6" t="s">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="D83" s="6"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="D84" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J83" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="J84" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="D86" s="6" t="s">
         <v>562</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>558</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="E88" s="6"/>
+        <v>562</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="J88" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>567</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="E89" s="6"/>
       <c r="J89" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B90" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="D90" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="D90" s="6" t="s">
-        <v>567</v>
-      </c>
       <c r="J90" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="E92" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E93" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J92" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="D94" s="6" t="s">
+      <c r="J93" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D95" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J94" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="J95" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="B98" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="D97" s="6" t="s">
         <v>583</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="E97" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E98" s="6"/>
-      <c r="J98" s="6" t="s">
-        <v>540</v>
+      <c r="J97" s="6" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="s">
-        <v>584</v>
+      <c r="A99" s="5" t="s">
+        <v>586</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>585</v>
-      </c>
-      <c r="E99" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="E99" s="6"/>
       <c r="J99" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D102" s="6" t="s">
         <v>589</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>585</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J102" s="6"/>
+      <c r="J102" s="6" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J103" s="6" t="s">
-        <v>540</v>
-      </c>
+      <c r="J103" s="6"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="D107" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="E106" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J107" s="6" t="s">
-        <v>540</v>
+      <c r="J106" s="6" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="s">
-        <v>599</v>
+      <c r="A108" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>601</v>
+        <v>81</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B110" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="D110" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="D110" s="6" t="s">
-        <v>601</v>
-      </c>
       <c r="J110" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>81</v>
+        <v>605</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="B114" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="D113" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="D114" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="E114" s="6" t="s">
+      <c r="E113" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J114" s="6" t="s">
-        <v>540</v>
+      <c r="J113" s="6" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AF168">
+  <conditionalFormatting sqref="A2:AF169">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$M2="accepted"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AB144">
+  <conditionalFormatting sqref="A2:AB145">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$M2="proposed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AB144">
+  <conditionalFormatting sqref="A2:AB145">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$M2="changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:C3 E2:E168 F2:J3 K2:K168 L2:L3 M2:O168 P2:AF3 A6:D168 F6:J168 L6:L168 P6:AF168">
+  <conditionalFormatting sqref="A2:C3 E2:E169 F2:J3 K2:K169 L2:L3 M2:O169 P2:AF3 A6:D169 F6:J169 L6:L169 P6:AF169">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>$M2="deprecated"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="rct_15" ref="J14"/>
+    <hyperlink r:id="rId1" location="rct_15" ref="J15"/>
   </hyperlinks>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -19089,16 +19364,16 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>19</v>
@@ -19107,7 +19382,7 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="6" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="41">
@@ -19136,10 +19411,244 @@
       <c r="AD2" s="7"/>
     </row>
     <row r="3">
-      <c r="K3" s="9"/>
+      <c r="A3" s="27" t="s">
+        <v>624</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>625</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="9">
+        <v>46062.0</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
     </row>
     <row r="4">
-      <c r="K4" s="9"/>
+      <c r="A4" s="27" t="s">
+        <v>629</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>630</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>632</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="9">
+        <v>46063.0</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="s">
+        <v>633</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>634</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>632</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="9">
+        <v>46064.0</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="s">
+        <v>636</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>637</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>632</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="9">
+        <v>46065.0</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="9">
+        <v>46062.0</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:AD141">
@@ -19228,16 +19737,16 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>19</v>
@@ -19278,17 +19787,17 @@
     </row>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
@@ -19328,17 +19837,17 @@
     </row>
     <row r="4">
       <c r="A4" s="27" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
@@ -19378,17 +19887,17 @@
     </row>
     <row r="5">
       <c r="A5" s="27" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
@@ -19428,17 +19937,17 @@
     </row>
     <row r="6">
       <c r="A6" s="27" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
@@ -19478,17 +19987,17 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="D7" s="35"/>
       <c r="E7" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
@@ -19528,17 +20037,17 @@
     </row>
     <row r="8">
       <c r="A8" s="27" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="D8" s="35"/>
       <c r="E8" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -19578,17 +20087,17 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
@@ -19627,20 +20136,20 @@
       <c r="AF9" s="26"/>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="s">
-        <v>646</v>
+      <c r="A10" s="44" t="s">
+        <v>667</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="C10" s="27" t="s">
+        <v>669</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>670</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>648</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>649</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>627</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
@@ -19679,20 +20188,20 @@
       <c r="AF10" s="26"/>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="s">
-        <v>650</v>
+      <c r="A11" s="44" t="s">
+        <v>671</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -19731,20 +20240,20 @@
       <c r="AF11" s="26"/>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="s">
-        <v>653</v>
+      <c r="A12" s="44" t="s">
+        <v>674</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
@@ -19784,17 +20293,17 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
@@ -19834,17 +20343,17 @@
     </row>
     <row r="14">
       <c r="A14" s="27" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="D14" s="35"/>
       <c r="E14" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -19884,17 +20393,17 @@
     </row>
     <row r="15">
       <c r="A15" s="27" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -19933,20 +20442,20 @@
       <c r="AF15" s="26"/>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="s">
-        <v>665</v>
+      <c r="A16" s="44" t="s">
+        <v>686</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -19965,7 +20474,7 @@
         <v>32</v>
       </c>
       <c r="N16" s="27" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="O16" s="26"/>
       <c r="P16" s="26"/>
@@ -19987,20 +20496,20 @@
       <c r="AF16" s="26"/>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="s">
-        <v>670</v>
+      <c r="A17" s="44" t="s">
+        <v>691</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -20039,20 +20548,20 @@
       <c r="AF17" s="26"/>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="s">
-        <v>673</v>
+      <c r="A18" s="44" t="s">
+        <v>694</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
@@ -20091,8 +20600,8 @@
       <c r="AF18" s="26"/>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="s">
-        <v>676</v>
+      <c r="A20" s="45" t="s">
+        <v>697</v>
       </c>
     </row>
   </sheetData>

--- a/code/vocab_csv/ai.xlsx
+++ b/code/vocab_csv/ai.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="1146">
   <si>
     <t>Term</t>
   </si>
@@ -1987,6 +1987,9 @@
   </si>
   <si>
     <t>This concept is a stub</t>
+  </si>
+  <si>
+    <t>deprecated</t>
   </si>
   <si>
     <t xml:space="preserve">BiasAssessment </t>
@@ -4746,16 +4749,16 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>205</v>
@@ -4775,7 +4778,7 @@
         <v>32</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O2" s="26"/>
       <c r="P2" s="26"/>
@@ -4798,16 +4801,16 @@
     </row>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>205</v>
@@ -4881,13 +4884,13 @@
     </row>
     <row r="5">
       <c r="A5" s="27" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="26" t="s">
@@ -4929,16 +4932,16 @@
     </row>
     <row r="6">
       <c r="A6" s="27" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>205</v>
@@ -4979,16 +4982,16 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>205</v>
@@ -5029,16 +5032,16 @@
     </row>
     <row r="8">
       <c r="A8" s="27" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>205</v>
@@ -5079,16 +5082,16 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>205</v>
@@ -5129,16 +5132,16 @@
     </row>
     <row r="10">
       <c r="A10" s="27" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>205</v>
@@ -5179,16 +5182,16 @@
     </row>
     <row r="11">
       <c r="A11" s="27" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>205</v>
@@ -5229,16 +5232,16 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="s">
+        <v>734</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>735</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>736</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>733</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>734</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>735</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>732</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>205</v>
@@ -5279,16 +5282,16 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>205</v>
@@ -5388,10 +5391,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
@@ -5423,23 +5426,23 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="46"/>
       <c r="G2" s="5" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2" s="46"/>
       <c r="I2" s="8"/>
@@ -5478,23 +5481,23 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
@@ -5567,23 +5570,23 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="26"/>
@@ -5621,23 +5624,23 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
@@ -5675,23 +5678,23 @@
     </row>
     <row r="8">
       <c r="A8" s="27" t="s">
+        <v>758</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>758</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>756</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
@@ -5729,23 +5732,23 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
@@ -5783,23 +5786,23 @@
     </row>
     <row r="10">
       <c r="A10" s="27" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
@@ -5837,22 +5840,22 @@
     </row>
     <row r="11">
       <c r="A11" s="27" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
@@ -5892,23 +5895,23 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
@@ -5946,23 +5949,23 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
@@ -6000,23 +6003,23 @@
     </row>
     <row r="14">
       <c r="A14" s="27" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -6054,23 +6057,23 @@
     </row>
     <row r="15">
       <c r="A15" s="27" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
@@ -6108,23 +6111,23 @@
     </row>
     <row r="16">
       <c r="A16" s="27" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
@@ -6162,22 +6165,22 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M17" s="9">
         <v>45627.0</v>
@@ -6194,23 +6197,23 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -6248,23 +6251,23 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -6302,23 +6305,23 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -6359,23 +6362,23 @@
     </row>
     <row r="22">
       <c r="A22" s="37" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -6413,23 +6416,23 @@
     </row>
     <row r="23">
       <c r="A23" s="27" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -6467,23 +6470,23 @@
     </row>
     <row r="24">
       <c r="A24" s="27" t="s">
+        <v>804</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>805</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="B24" s="27" t="s">
-        <v>804</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>802</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -6521,23 +6524,23 @@
     </row>
     <row r="25">
       <c r="A25" s="27" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -6575,23 +6578,23 @@
     </row>
     <row r="26">
       <c r="A26" s="27" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -6629,22 +6632,22 @@
     </row>
     <row r="27">
       <c r="A27" s="27" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M27" s="9">
         <v>45627.0</v>
@@ -6661,23 +6664,23 @@
     </row>
     <row r="28">
       <c r="A28" s="27" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -6715,23 +6718,23 @@
     </row>
     <row r="29">
       <c r="A29" s="27" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -6769,23 +6772,23 @@
     </row>
     <row r="30">
       <c r="A30" s="27" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -6823,23 +6826,23 @@
     </row>
     <row r="31">
       <c r="A31" s="27" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -6877,23 +6880,23 @@
     </row>
     <row r="32">
       <c r="A32" s="27" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -6931,22 +6934,22 @@
     </row>
     <row r="33">
       <c r="A33" s="27" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M33" s="9">
         <v>45627.0</v>
@@ -6963,23 +6966,23 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -7017,23 +7020,23 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -7071,23 +7074,23 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
@@ -7129,23 +7132,23 @@
     </row>
     <row r="38">
       <c r="A38" s="37" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
@@ -7183,23 +7186,23 @@
     </row>
     <row r="39">
       <c r="A39" s="27" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -7237,23 +7240,23 @@
     </row>
     <row r="40">
       <c r="A40" s="27" t="s">
+        <v>850</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>851</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>849</v>
       </c>
-      <c r="B40" s="27" t="s">
-        <v>850</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>851</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>848</v>
-      </c>
       <c r="E40" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -7291,23 +7294,23 @@
     </row>
     <row r="41">
       <c r="A41" s="27" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -7345,23 +7348,23 @@
     </row>
     <row r="42">
       <c r="A42" s="27" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -7399,22 +7402,22 @@
     </row>
     <row r="43">
       <c r="A43" s="27" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M43" s="9">
         <v>45627.0</v>
@@ -7431,23 +7434,23 @@
     </row>
     <row r="44">
       <c r="A44" s="27" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -7485,23 +7488,23 @@
     </row>
     <row r="45">
       <c r="A45" s="27" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -7539,23 +7542,23 @@
     </row>
     <row r="46">
       <c r="A46" s="27" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
@@ -7593,23 +7596,23 @@
     </row>
     <row r="47">
       <c r="A47" s="27" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -7647,23 +7650,23 @@
     </row>
     <row r="48">
       <c r="A48" s="27" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
@@ -7701,22 +7704,22 @@
     </row>
     <row r="49">
       <c r="A49" s="27" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M49" s="9">
         <v>45627.0</v>
@@ -7733,23 +7736,23 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
@@ -7787,23 +7790,23 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
@@ -7841,23 +7844,23 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
@@ -7898,23 +7901,23 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -7952,26 +7955,26 @@
     </row>
     <row r="55">
       <c r="A55" s="27" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F55" s="26"/>
       <c r="G55" s="27" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I55" s="26"/>
       <c r="J55" s="26"/>
@@ -8008,26 +8011,26 @@
     </row>
     <row r="56">
       <c r="A56" s="27" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F56" s="26"/>
       <c r="G56" s="27" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H56" s="27" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I56" s="26"/>
       <c r="J56" s="26"/>
@@ -8064,31 +8067,31 @@
     </row>
     <row r="57">
       <c r="A57" s="27" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F57" s="26"/>
       <c r="G57" s="27" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
       <c r="K57" s="6" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L57" s="26"/>
       <c r="M57" s="9">
@@ -8122,31 +8125,31 @@
     </row>
     <row r="58">
       <c r="A58" s="27" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F58" s="26"/>
       <c r="G58" s="27" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I58" s="26"/>
       <c r="J58" s="26"/>
       <c r="K58" s="30" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L58" s="26"/>
       <c r="M58" s="9">
@@ -8183,23 +8186,23 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
@@ -8240,23 +8243,23 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
@@ -8297,23 +8300,23 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
@@ -8351,23 +8354,23 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C66" s="47" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F66" s="11"/>
       <c r="G66" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H66" s="11"/>
       <c r="K66" s="11"/>
@@ -8380,7 +8383,7 @@
         <v>21</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
@@ -8403,28 +8406,28 @@
     </row>
     <row r="67">
       <c r="A67" s="47" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B67" s="47" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F67" s="11"/>
       <c r="G67" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H67" s="11"/>
       <c r="K67" s="11"/>
       <c r="L67" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M67" s="49">
         <v>45548.0</v>
@@ -8436,7 +8439,7 @@
         <v>32</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
@@ -8457,28 +8460,28 @@
     </row>
     <row r="68">
       <c r="A68" s="47" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B68" s="47" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D68" s="48" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F68" s="11"/>
       <c r="G68" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H68" s="11"/>
       <c r="K68" s="11"/>
       <c r="L68" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M68" s="49">
         <v>45548.0</v>
@@ -8488,7 +8491,7 @@
         <v>21</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
@@ -8511,28 +8514,28 @@
     </row>
     <row r="69">
       <c r="A69" s="48" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F69" s="11"/>
       <c r="G69" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H69" s="11"/>
       <c r="K69" s="11"/>
       <c r="L69" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M69" s="49">
         <v>45548.0</v>
@@ -8544,7 +8547,7 @@
         <v>32</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q69" s="11"/>
       <c r="R69" s="11"/>
@@ -8565,28 +8568,28 @@
     </row>
     <row r="70">
       <c r="A70" s="47" t="s">
+        <v>937</v>
+      </c>
+      <c r="B70" s="47" t="s">
+        <v>938</v>
+      </c>
+      <c r="C70" s="47" t="s">
+        <v>939</v>
+      </c>
+      <c r="D70" s="48" t="s">
         <v>936</v>
       </c>
-      <c r="B70" s="47" t="s">
-        <v>937</v>
-      </c>
-      <c r="C70" s="47" t="s">
-        <v>938</v>
-      </c>
-      <c r="D70" s="48" t="s">
-        <v>935</v>
-      </c>
       <c r="E70" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F70" s="11"/>
       <c r="G70" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H70" s="11"/>
       <c r="K70" s="11"/>
       <c r="L70" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M70" s="49">
         <v>45548.0</v>
@@ -8596,7 +8599,7 @@
         <v>21</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q70" s="11"/>
       <c r="R70" s="11"/>
@@ -8619,30 +8622,30 @@
     </row>
     <row r="71">
       <c r="A71" s="48" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D71" s="48" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F71" s="11"/>
       <c r="G71" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H71" s="11"/>
       <c r="K71" s="47" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="L71" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M71" s="49">
         <v>45548.0</v>
@@ -8654,7 +8657,7 @@
         <v>32</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q71" s="11"/>
       <c r="R71" s="11"/>
@@ -8675,28 +8678,28 @@
     </row>
     <row r="72">
       <c r="A72" s="47" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B72" s="47" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C72" s="47" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F72" s="11"/>
       <c r="G72" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H72" s="11"/>
       <c r="K72" s="11"/>
       <c r="L72" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M72" s="49">
         <v>45548.0</v>
@@ -8706,7 +8709,7 @@
         <v>21</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q72" s="11"/>
       <c r="R72" s="11"/>
@@ -8729,28 +8732,28 @@
     </row>
     <row r="73">
       <c r="A73" s="47" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B73" s="47" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F73" s="11"/>
       <c r="G73" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H73" s="11"/>
       <c r="K73" s="11"/>
       <c r="L73" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M73" s="49">
         <v>45548.0</v>
@@ -8760,7 +8763,7 @@
         <v>21</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q73" s="11"/>
       <c r="R73" s="11"/>
@@ -8783,30 +8786,30 @@
     </row>
     <row r="74">
       <c r="A74" s="47" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B74" s="47" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C74" s="47" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D74" s="48" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F74" s="11"/>
       <c r="G74" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H74" s="11"/>
       <c r="K74" s="47" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="L74" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M74" s="49">
         <v>45548.0</v>
@@ -8816,7 +8819,7 @@
         <v>21</v>
       </c>
       <c r="P74" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q74" s="11"/>
       <c r="R74" s="11"/>
@@ -8839,28 +8842,28 @@
     </row>
     <row r="75">
       <c r="A75" s="47" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B75" s="47" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F75" s="11"/>
       <c r="G75" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H75" s="11"/>
       <c r="K75" s="11"/>
       <c r="L75" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M75" s="49">
         <v>45548.0</v>
@@ -8870,7 +8873,7 @@
         <v>21</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q75" s="11"/>
       <c r="R75" s="11"/>
@@ -8893,28 +8896,28 @@
     </row>
     <row r="76">
       <c r="A76" s="47" t="s">
+        <v>958</v>
+      </c>
+      <c r="B76" s="47" t="s">
+        <v>959</v>
+      </c>
+      <c r="C76" s="47" t="s">
+        <v>960</v>
+      </c>
+      <c r="D76" s="48" t="s">
         <v>957</v>
       </c>
-      <c r="B76" s="47" t="s">
-        <v>958</v>
-      </c>
-      <c r="C76" s="47" t="s">
-        <v>959</v>
-      </c>
-      <c r="D76" s="48" t="s">
-        <v>956</v>
-      </c>
       <c r="E76" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F76" s="11"/>
       <c r="G76" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H76" s="11"/>
       <c r="K76" s="11"/>
       <c r="L76" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M76" s="49">
         <v>45548.0</v>
@@ -8924,7 +8927,7 @@
         <v>21</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q76" s="11"/>
       <c r="R76" s="11"/>
@@ -8947,28 +8950,28 @@
     </row>
     <row r="77">
       <c r="A77" s="47" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B77" s="47" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F77" s="11"/>
       <c r="G77" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H77" s="11"/>
       <c r="K77" s="11"/>
       <c r="L77" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M77" s="49">
         <v>45548.0</v>
@@ -8978,7 +8981,7 @@
         <v>21</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q77" s="11"/>
       <c r="R77" s="11"/>
@@ -9001,30 +9004,30 @@
     </row>
     <row r="78">
       <c r="A78" s="47" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B78" s="47" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C78" s="47" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F78" s="11"/>
       <c r="G78" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H78" s="11"/>
       <c r="K78" s="47" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="L78" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M78" s="49">
         <v>45548.0</v>
@@ -9034,7 +9037,7 @@
         <v>21</v>
       </c>
       <c r="P78" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q78" s="11"/>
       <c r="R78" s="11"/>
@@ -9057,28 +9060,28 @@
     </row>
     <row r="79">
       <c r="A79" s="47" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B79" s="47" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C79" s="47" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F79" s="11"/>
       <c r="G79" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H79" s="11"/>
       <c r="K79" s="11"/>
       <c r="L79" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M79" s="49">
         <v>45548.0</v>
@@ -9088,7 +9091,7 @@
         <v>21</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q79" s="11"/>
       <c r="R79" s="11"/>
@@ -9111,28 +9114,28 @@
     </row>
     <row r="80">
       <c r="A80" s="47" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B80" s="47" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D80" s="48" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F80" s="11"/>
       <c r="G80" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H80" s="11"/>
       <c r="K80" s="11"/>
       <c r="L80" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M80" s="49">
         <v>45548.0</v>
@@ -9142,7 +9145,7 @@
         <v>21</v>
       </c>
       <c r="P80" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q80" s="11"/>
       <c r="R80" s="11"/>
@@ -9165,28 +9168,28 @@
     </row>
     <row r="81">
       <c r="A81" s="47" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B81" s="47" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D81" s="48" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F81" s="11"/>
       <c r="G81" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H81" s="11"/>
       <c r="K81" s="11"/>
       <c r="L81" s="47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M81" s="49">
         <v>45548.0</v>
@@ -9196,7 +9199,7 @@
         <v>21</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q81" s="11"/>
       <c r="R81" s="11"/>
@@ -9219,21 +9222,21 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B83" s="42" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C83" s="42" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F83" s="7"/>
       <c r="G83" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
@@ -9271,16 +9274,16 @@
     </row>
     <row r="85">
       <c r="A85" s="27" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C85" s="42" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E85" s="26"/>
       <c r="F85" s="26"/>
@@ -9288,19 +9291,19 @@
       <c r="H85" s="26"/>
       <c r="I85" s="26"/>
       <c r="J85" s="26" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="27" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C86" s="26"/>
       <c r="D86" s="26" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E86" s="26"/>
       <c r="F86" s="26"/>
@@ -9308,27 +9311,27 @@
       <c r="H86" s="26"/>
       <c r="I86" s="26"/>
       <c r="J86" s="26" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="27" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C87" s="26"/>
       <c r="D87" s="26"/>
       <c r="E87" s="26"/>
       <c r="F87" s="26"/>
       <c r="G87" s="27" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H87" s="26"/>
       <c r="I87" s="26"/>
       <c r="J87" s="26" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
   </sheetData>
@@ -9417,25 +9420,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="40" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>91</v>
@@ -9443,13 +9446,13 @@
     </row>
     <row r="2">
       <c r="A2" s="50" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D2" s="52"/>
       <c r="E2" s="6" t="s">
@@ -9458,16 +9461,16 @@
     </row>
     <row r="3">
       <c r="A3" s="53" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>85</v>
@@ -9476,24 +9479,24 @@
         <v>214</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="53" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>85</v>
@@ -9502,21 +9505,21 @@
         <v>309</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="53" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>85</v>
@@ -9525,24 +9528,24 @@
         <v>85</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>85</v>
@@ -9551,47 +9554,47 @@
         <v>85</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B7" s="40" t="s">
         <v>311</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>81</v>
@@ -9600,7 +9603,7 @@
         <v>475</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>515</v>
@@ -9608,16 +9611,16 @@
     </row>
     <row r="9">
       <c r="A9" s="53" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>513</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>81</v>
@@ -9626,47 +9629,47 @@
         <v>81</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>473</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B11" s="40" t="s">
         <v>517</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>81</v>
@@ -9675,24 +9678,24 @@
         <v>81</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="53" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>81</v>
@@ -9701,24 +9704,24 @@
         <v>81</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="53" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B13" s="40" t="s">
         <v>434</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>81</v>
@@ -9727,21 +9730,21 @@
         <v>425</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="53" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B14" s="40" t="s">
         <v>437</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D14" s="40" t="s">
         <v>434</v>
@@ -9753,21 +9756,21 @@
         <v>81</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="53" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>407</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D15" s="40" t="s">
         <v>434</v>
@@ -9779,12 +9782,12 @@
         <v>425</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="53" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B16" s="40" t="s">
         <v>427</v>
@@ -9799,21 +9802,21 @@
         <v>81</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="53" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D17" s="40" t="s">
         <v>407</v>
@@ -9822,21 +9825,21 @@
         <v>81</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="53" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>430</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D18" s="40" t="s">
         <v>407</v>
@@ -9845,21 +9848,21 @@
         <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="53" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B19" s="40" t="s">
         <v>441</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D19" s="40" t="s">
         <v>407</v>
@@ -9871,21 +9874,21 @@
         <v>81</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="53" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B20" s="40" t="s">
         <v>444</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D20" s="40" t="s">
         <v>407</v>
@@ -9894,21 +9897,21 @@
         <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="53" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B21" s="40" t="s">
         <v>447</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D21" s="40" t="s">
         <v>407</v>
@@ -9920,21 +9923,21 @@
         <v>81</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="53" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B22" s="40" t="s">
         <v>450</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D22" s="40" t="s">
         <v>407</v>
@@ -9943,27 +9946,27 @@
         <v>81</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="53" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B23" s="40" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>81</v>
@@ -9972,21 +9975,21 @@
         <v>81</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="53" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B24" s="40" t="s">
         <v>162</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D24" s="40" t="s">
         <v>47</v>
@@ -9998,15 +10001,15 @@
         <v>72</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="53" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B25" s="40" t="s">
         <v>404</v>
@@ -10024,21 +10027,21 @@
         <v>357</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>208</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>85</v>
@@ -10046,13 +10049,13 @@
     </row>
     <row r="28">
       <c r="A28" s="53" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B28" s="40" t="s">
         <v>218</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D28" s="40" t="s">
         <v>208</v>
@@ -10064,18 +10067,18 @@
         <v>223</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="53" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D29" s="40" t="s">
         <v>218</v>
@@ -10087,18 +10090,18 @@
         <v>261</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="53" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>222</v>
@@ -10113,21 +10116,21 @@
         <v>223</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="53" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B31" s="40" t="s">
         <v>233</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D31" s="40" t="s">
         <v>208</v>
@@ -10136,18 +10139,18 @@
         <v>85</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="53" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D32" s="40" t="s">
         <v>233</v>
@@ -10156,18 +10159,18 @@
         <v>85</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="53" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D33" s="40" t="s">
         <v>233</v>
@@ -10176,18 +10179,18 @@
         <v>85</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="53" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B34" s="40" t="s">
         <v>236</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D34" s="40" t="s">
         <v>208</v>
@@ -10196,18 +10199,18 @@
         <v>85</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="53" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D35" s="40" t="s">
         <v>208</v>
@@ -10216,21 +10219,21 @@
         <v>85</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="53" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D36" s="40" t="s">
         <v>208</v>
@@ -10242,21 +10245,21 @@
         <v>214</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="53" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B37" s="40" t="s">
         <v>225</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D37" s="40" t="s">
         <v>208</v>
@@ -10265,18 +10268,18 @@
         <v>85</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D39" s="52"/>
       <c r="E39" s="6" t="s">
@@ -10285,16 +10288,16 @@
     </row>
     <row r="40">
       <c r="A40" s="53" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>67</v>
@@ -10303,24 +10306,24 @@
         <v>67</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="53" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B41" s="40" t="s">
         <v>133</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>67</v>
@@ -10329,50 +10332,50 @@
         <v>67</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="53" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B42" s="40" t="s">
         <v>100</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>67</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="53" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B43" s="40" t="s">
         <v>136</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>67</v>
@@ -10381,24 +10384,24 @@
         <v>67</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="53" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B44" s="40" t="s">
         <v>138</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>67</v>
@@ -10407,24 +10410,24 @@
         <v>117</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="53" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B45" s="40" t="s">
         <v>141</v>
       </c>
       <c r="C45" s="40" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>67</v>
@@ -10433,24 +10436,24 @@
         <v>67</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="53" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B46" s="40" t="s">
         <v>144</v>
       </c>
       <c r="C46" s="40" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D46" s="40" t="s">
         <v>138</v>
@@ -10462,34 +10465,34 @@
         <v>67</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B48" s="54" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B49" s="54" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="40" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C50" s="40"/>
       <c r="D50" s="40"/>
@@ -10502,215 +10505,215 @@
     </row>
     <row r="52">
       <c r="A52" s="40" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C52" s="40"/>
       <c r="D52" s="40" t="s">
+        <v>993</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>992</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="53" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C53" s="52"/>
       <c r="D53" s="52"/>
       <c r="E53" s="40" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="53" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C54" s="40"/>
       <c r="D54" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="53" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C55" s="40"/>
       <c r="D55" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="53" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="40"/>
       <c r="D56" s="40" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="53" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C57" s="40"/>
       <c r="D57" s="40" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="53" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B58" s="40" t="s">
         <v>311</v>
       </c>
       <c r="C58" s="40"/>
       <c r="D58" s="40" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="53" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C59" s="40"/>
       <c r="D59" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="53" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B60" s="40" t="s">
         <v>513</v>
       </c>
       <c r="C60" s="40"/>
       <c r="D60" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="53" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B61" s="40" t="s">
         <v>473</v>
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="53" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B62" s="40" t="s">
         <v>517</v>
       </c>
       <c r="C62" s="40"/>
       <c r="D62" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="53" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B63" s="40" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C63" s="40"/>
       <c r="D63" s="40" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="53" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B64" s="40" t="s">
         <v>434</v>
       </c>
       <c r="C64" s="40"/>
       <c r="D64" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="53" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B65" s="40" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C65" s="40"/>
       <c r="D65" s="40" t="s">
         <v>434</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="53" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B66" s="40" t="s">
         <v>407</v>
@@ -10720,12 +10723,12 @@
         <v>434</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="53" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B67" s="40" t="s">
         <v>427</v>
@@ -10740,22 +10743,22 @@
     </row>
     <row r="68">
       <c r="A68" s="53" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B68" s="40" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C68" s="40"/>
       <c r="D68" s="40" t="s">
         <v>407</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="53" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B69" s="40" t="s">
         <v>430</v>
@@ -10765,12 +10768,12 @@
         <v>407</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="53" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B70" s="40" t="s">
         <v>441</v>
@@ -10780,12 +10783,12 @@
         <v>407</v>
       </c>
       <c r="E70" s="40" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="53" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B71" s="40" t="s">
         <v>444</v>
@@ -10795,12 +10798,12 @@
         <v>407</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="53" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B72" s="40" t="s">
         <v>447</v>
@@ -10810,12 +10813,12 @@
         <v>407</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="53" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B73" s="40" t="s">
         <v>450</v>
@@ -10825,42 +10828,42 @@
         <v>407</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="53" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B74" s="40" t="s">
         <v>47</v>
       </c>
       <c r="C74" s="40"/>
       <c r="D74" s="40" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="53" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B75" s="40" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C75" s="40"/>
       <c r="D75" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="53" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B76" s="40" t="s">
         <v>404</v>
@@ -10875,7 +10878,7 @@
     </row>
     <row r="77">
       <c r="A77" s="53" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B77" s="40" t="s">
         <v>208</v>
@@ -10883,12 +10886,12 @@
       <c r="C77" s="52"/>
       <c r="D77" s="52"/>
       <c r="E77" s="40" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="53" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B78" s="40" t="s">
         <v>218</v>
@@ -10898,30 +10901,30 @@
         <v>208</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="53" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B79" s="40" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C79" s="40"/>
       <c r="D79" s="40" t="s">
         <v>218</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="53" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="40" t="s">
@@ -10933,7 +10936,7 @@
     </row>
     <row r="81">
       <c r="A81" s="53" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B81" s="40" t="s">
         <v>233</v>
@@ -10943,42 +10946,42 @@
         <v>208</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="53" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C82" s="40"/>
       <c r="D82" s="40" t="s">
         <v>233</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="53" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B83" s="40" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C83" s="40"/>
       <c r="D83" s="40" t="s">
         <v>233</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="53" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B84" s="40" t="s">
         <v>236</v>
@@ -10988,42 +10991,42 @@
         <v>208</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="53" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C85" s="40"/>
       <c r="D85" s="40" t="s">
         <v>208</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="53" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C86" s="40"/>
       <c r="D86" s="40" t="s">
         <v>208</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="53" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B87" s="40" t="s">
         <v>225</v>
@@ -11033,115 +11036,115 @@
         <v>208</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="53" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B88" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C88" s="52"/>
       <c r="D88" s="52"/>
       <c r="E88" s="40" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="53" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B89" s="40" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C89" s="40"/>
       <c r="D89" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="53" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B90" s="40" t="s">
         <v>133</v>
       </c>
       <c r="C90" s="40"/>
       <c r="D90" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="53" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B91" s="40" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="40"/>
       <c r="D91" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="53" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B92" s="40" t="s">
         <v>136</v>
       </c>
       <c r="C92" s="40"/>
       <c r="D92" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="53" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B93" s="40" t="s">
         <v>138</v>
       </c>
       <c r="C93" s="40"/>
       <c r="D93" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="53" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B94" s="40" t="s">
         <v>141</v>
       </c>
       <c r="C94" s="40"/>
       <c r="D94" s="40" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="53" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B95" s="40" t="s">
         <v>144</v>
@@ -11151,7 +11154,7 @@
         <v>138</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -19378,53 +19381,33 @@
       <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
       <c r="I2" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="J2" s="7"/>
       <c r="K2" s="41">
         <v>45410.0</v>
       </c>
-      <c r="L2" s="7"/>
       <c r="M2" s="6" t="s">
-        <v>21</v>
+        <v>624</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
     </row>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -19460,19 +19443,19 @@
     </row>
     <row r="4">
       <c r="A4" s="27" t="s">
+        <v>630</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>631</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>633</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>629</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>630</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>631</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>632</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>628</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -19508,19 +19491,19 @@
     </row>
     <row r="5">
       <c r="A5" s="27" t="s">
+        <v>634</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>635</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>636</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>633</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>634</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>635</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>632</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -19556,19 +19539,19 @@
     </row>
     <row r="6">
       <c r="A6" s="27" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -19604,19 +19587,19 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -19737,16 +19720,16 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>19</v>
@@ -19787,17 +19770,17 @@
     </row>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
@@ -19837,17 +19820,17 @@
     </row>
     <row r="4">
       <c r="A4" s="27" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
@@ -19887,17 +19870,17 @@
     </row>
     <row r="5">
       <c r="A5" s="27" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
@@ -19937,17 +19920,17 @@
     </row>
     <row r="6">
       <c r="A6" s="27" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
@@ -19987,17 +19970,17 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D7" s="35"/>
       <c r="E7" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
@@ -20037,17 +20020,17 @@
     </row>
     <row r="8">
       <c r="A8" s="27" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D8" s="35"/>
       <c r="E8" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -20087,17 +20070,17 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
@@ -20137,19 +20120,19 @@
     </row>
     <row r="10">
       <c r="A10" s="44" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
@@ -20189,19 +20172,19 @@
     </row>
     <row r="11">
       <c r="A11" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>673</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>674</v>
+      </c>
+      <c r="D11" s="35" t="s">
         <v>671</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>672</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>673</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>670</v>
-      </c>
       <c r="E11" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -20241,19 +20224,19 @@
     </row>
     <row r="12">
       <c r="A12" s="44" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
@@ -20293,17 +20276,17 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
@@ -20343,17 +20326,17 @@
     </row>
     <row r="14">
       <c r="A14" s="27" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D14" s="35"/>
       <c r="E14" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -20393,17 +20376,17 @@
     </row>
     <row r="15">
       <c r="A15" s="27" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -20443,19 +20426,19 @@
     </row>
     <row r="16">
       <c r="A16" s="44" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -20474,7 +20457,7 @@
         <v>32</v>
       </c>
       <c r="N16" s="27" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O16" s="26"/>
       <c r="P16" s="26"/>
@@ -20497,19 +20480,19 @@
     </row>
     <row r="17">
       <c r="A17" s="44" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -20549,19 +20532,19 @@
     </row>
     <row r="18">
       <c r="A18" s="44" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
@@ -20601,7 +20584,7 @@
     </row>
     <row r="20">
       <c r="A20" s="45" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
